--- a/Vessel_Event_Revenue_Recon_FY26.xlsx
+++ b/Vessel_Event_Revenue_Recon_FY26.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Per-Event Revenue" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Daily Recon" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Category Recon" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="PMIX NA Breakout" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="243">
   <si>
     <t xml:space="preserve">Vessel</t>
   </si>
@@ -75,6 +76,15 @@
     <t xml:space="preserve">TOTAL REVENUE</t>
   </si>
   <si>
+    <t xml:space="preserve">Food $ / person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bev $ / person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total $ / person</t>
+  </si>
+  <si>
     <t xml:space="preserve">Svc Chg / Fees</t>
   </si>
   <si>
@@ -555,7 +565,7 @@
     <t xml:space="preserve">1. BEO revenue components tie to Tripleseat "Event Actual" for all 97 events; the rental fee is included in Event Actual for some events and booked as a fee for others — resolved per event so every row ties.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. NA BEVERAGE: BEOs book only $875 as NA, but Toast rings $57,645 — NA drinks at events are folded into bar packages/consumption tabs on the BEO, and rung individually in POS. Category-level BEO-vs-POS food/alcohol comparisons are distorted by this.</t>
+    <t xml:space="preserve">2. NA BEVERAGE: BEOs book only $875 as NA and Toast shows $57,645 — but the PMIX NA Breakout tab proves the Toast figure is mislabeled: ~88% of it is alcohol bar packages/open bars rung as open items under the NA sales category (true NA is only ~$4.3K). Fix the open-item button mapping in Toast.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Toast net sales are AFTER $22,309 of POS discounts (incl. $15,829 Manager Comp — check level); BEO actuals are pre-discount. This depresses Toast vs BEO in the map above.</t>
@@ -568,16 +578,192 @@
   </si>
   <si>
     <t xml:space="preserve">6. Walk-in/bar-only days total $16,888 across 45 dates with no event booked — the open-night bar business, in Toast but never on a BEO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is really inside Toast "NA Beverage" — FY26 PMIX item detail (net item amounts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item rung under NA Beverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reclass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Ho Package  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol / bar package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Bar  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port Of Call Package  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port Of Call Open Bar  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port Of Call Third Hour  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchors Away  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol Package  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just Frens Bar  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverage Station  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True NA beverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialty Bottles  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Salad  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food (mis-rung)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drink Tickets  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid Beverages  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Drink Package  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmon with White Wine Sauce  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wine Bottle  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverages On Consumption  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverages  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosecco Welcome  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM Beverage Station  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepaid Beverages On Consumption  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosecco  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continenal Breakfast  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half Day Beverage Station  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosecco Toast  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottle Of Bourbon Client Gift  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vip  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other / unclear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemoncello  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rittenhouse Rye  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long Island  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mai Tai  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint Condition  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natty Boh  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH Riesling  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Fashion Happy Hour  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip  (open item)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All NA-categorized MENU items (sodas, water, juice, mocktails, espresso…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL RUNG AS "NA BEVERAGE" (PMIX basis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECLASSED SUMMARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED FY BEVERAGE SPLIT (Toast, PMIX basis): Alcohol = Liquor+Wine+Beer as rung + NA-bucket alcohol reclass; NA = true NA only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverage — Alcohol (corrected)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverage — NA (corrected)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unclear beverage rings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEO comparison — Alcoholic Beverage (Tripleseat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEO comparison — NA Beverage (Tripleseat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toast "NA Beverage" is NOT an NA number at Vessel: bar packages, open bars, prosecco and drink tickets are rung as open items under the NA sales category.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of the NA bucket, only ~7% is true NA beverage. Fix: assign open-item buttons (bar packages, on-consumption bars) to Liquor, and food packages to Food.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMIX basis = net item amounts; excludes the $25,176 of Non-Grat Svc Charges and minor deferred/void basis differences vs the Sales Summary category table.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -718,7 +904,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -759,6 +945,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -767,7 +957,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -796,6 +994,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1051,7 +1253,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:U104"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1059,7 +1261,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="6" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1127,19 +1329,28 @@
       <c r="R4" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="S4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>45841</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>175</v>
@@ -1177,13 +1388,25 @@
         <f aca="false">K5+L5+M5+N5</f>
         <v>7288.38</v>
       </c>
-      <c r="P5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+      <c r="P5" s="10" t="n">
+        <f aca="false">IF(N(E5)&gt;0,G5/E5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <f aca="false">IF(N(E5)&gt;0,J5/E5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <f aca="false">IF(N(E5)&gt;0,O5/E5,"")</f>
+        <v>41.6478857142857</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="8" t="n">
         <v>7288.38</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="U5" s="8" t="n">
         <v>7288.38</v>
       </c>
     </row>
@@ -1192,13 +1415,13 @@
         <v>45843</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>85</v>
@@ -1236,13 +1459,25 @@
         <f aca="false">K6+L6+M6+N6</f>
         <v>7931.52</v>
       </c>
-      <c r="P6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8" t="n">
+      <c r="P6" s="10" t="n">
+        <f aca="false">IF(N(E6)&gt;0,G6/E6,"")</f>
+        <v>26.2941176470588</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <f aca="false">IF(N(E6)&gt;0,J6/E6,"")</f>
+        <v>67.0178823529412</v>
+      </c>
+      <c r="R6" s="10" t="n">
+        <f aca="false">IF(N(E6)&gt;0,O6/E6,"")</f>
+        <v>93.312</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8" t="n">
         <v>7265.62</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="U6" s="8" t="n">
         <v>8468.9</v>
       </c>
     </row>
@@ -1251,13 +1486,13 @@
         <v>45849</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>25</v>
@@ -1295,13 +1530,25 @@
         <f aca="false">K7+L7+M7+N7</f>
         <v>0</v>
       </c>
-      <c r="P7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8" t="n">
+      <c r="P7" s="10" t="n">
+        <f aca="false">IF(N(E7)&gt;0,G7/E7,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10" t="n">
+        <f aca="false">IF(N(E7)&gt;0,J7/E7,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="10" t="n">
+        <f aca="false">IF(N(E7)&gt;0,O7/E7,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8" t="n">
         <v>774.6</v>
       </c>
     </row>
@@ -1310,13 +1557,13 @@
         <v>45849</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>20</v>
@@ -1354,10 +1601,22 @@
         <f aca="false">K8+L8+M8+N8</f>
         <v>1050</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+      <c r="P8" s="10" t="n">
+        <f aca="false">IF(N(E8)&gt;0,G8/E8,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <f aca="false">IF(N(E8)&gt;0,J8/E8,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="10" t="n">
+        <f aca="false">IF(N(E8)&gt;0,O8/E8,"")</f>
+        <v>52.5</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="8" t="n">
         <v>1092</v>
       </c>
     </row>
@@ -1366,13 +1625,13 @@
         <v>45856</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>50</v>
@@ -1410,13 +1669,25 @@
         <f aca="false">K9+L9+M9+N9</f>
         <v>2500</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="P9" s="10" t="n">
+        <f aca="false">IF(N(E9)&gt;0,G9/E9,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <f aca="false">IF(N(E9)&gt;0,J9/E9,"")</f>
+        <v>50</v>
+      </c>
+      <c r="R9" s="10" t="n">
+        <f aca="false">IF(N(E9)&gt;0,O9/E9,"")</f>
+        <v>50</v>
+      </c>
+      <c r="S9" s="8" t="n">
         <v>625</v>
       </c>
-      <c r="Q9" s="8" t="n">
+      <c r="T9" s="8" t="n">
         <v>3282.5</v>
       </c>
-      <c r="R9" s="8" t="n">
+      <c r="U9" s="8" t="n">
         <v>3396</v>
       </c>
     </row>
@@ -1425,13 +1696,13 @@
         <v>45860</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>55</v>
@@ -1469,13 +1740,25 @@
         <f aca="false">K10+L10+M10+N10</f>
         <v>4910</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="P10" s="10" t="n">
+        <f aca="false">IF(N(E10)&gt;0,G10/E10,"")</f>
+        <v>7.27272727272727</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <f aca="false">IF(N(E10)&gt;0,J10/E10,"")</f>
+        <v>72</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <f aca="false">IF(N(E10)&gt;0,O10/E10,"")</f>
+        <v>89.2727272727273</v>
+      </c>
+      <c r="S10" s="8" t="n">
         <v>982</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="T10" s="8" t="n">
         <v>5882</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="U10" s="8" t="n">
         <v>5535.9</v>
       </c>
     </row>
@@ -1484,13 +1767,13 @@
         <v>45861</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>55</v>
@@ -1528,10 +1811,22 @@
         <f aca="false">K11+L11+M11+N11</f>
         <v>4690</v>
       </c>
-      <c r="P11" s="8" t="n">
+      <c r="P11" s="10" t="n">
+        <f aca="false">IF(N(E11)&gt;0,G11/E11,"")</f>
+        <v>75.2727272727273</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <f aca="false">IF(N(E11)&gt;0,J11/E11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <f aca="false">IF(N(E11)&gt;0,O11/E11,"")</f>
+        <v>85.2727272727273</v>
+      </c>
+      <c r="S11" s="8" t="n">
         <v>1172.5</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="T11" s="8" t="n">
         <v>6110.9</v>
       </c>
     </row>
@@ -1540,13 +1835,13 @@
         <v>45862</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>55</v>
@@ -1584,13 +1879,25 @@
         <f aca="false">K12+L12+M12+N12</f>
         <v>2250</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="P12" s="10" t="n">
+        <f aca="false">IF(N(E12)&gt;0,G12/E12,"")</f>
+        <v>30.9090909090909</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <f aca="false">IF(N(E12)&gt;0,J12/E12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <f aca="false">IF(N(E12)&gt;0,O12/E12,"")</f>
+        <v>40.9090909090909</v>
+      </c>
+      <c r="S12" s="8" t="n">
         <v>562.5</v>
       </c>
-      <c r="Q12" s="8" t="n">
+      <c r="T12" s="8" t="n">
         <v>2914.5</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="U12" s="8" t="n">
         <v>7287</v>
       </c>
     </row>
@@ -1599,13 +1906,13 @@
         <v>45863</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>160</v>
@@ -1643,13 +1950,25 @@
         <f aca="false">K13+L13+M13+N13</f>
         <v>7063.82</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8" t="n">
+      <c r="P13" s="10" t="n">
+        <f aca="false">IF(N(E13)&gt;0,G13/E13,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <f aca="false">IF(N(E13)&gt;0,J13/E13,"")</f>
+        <v>8.848875</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <f aca="false">IF(N(E13)&gt;0,O13/E13,"")</f>
+        <v>44.148875</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="8" t="n">
         <v>7191.24</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="U13" s="8" t="n">
         <v>5648</v>
       </c>
     </row>
@@ -1658,13 +1977,13 @@
         <v>45865</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>75</v>
@@ -1702,13 +2021,25 @@
         <f aca="false">K14+L14+M14+N14</f>
         <v>2250</v>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="P14" s="10" t="n">
+        <f aca="false">IF(N(E14)&gt;0,G14/E14,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <f aca="false">IF(N(E14)&gt;0,J14/E14,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <f aca="false">IF(N(E14)&gt;0,O14/E14,"")</f>
+        <v>30</v>
+      </c>
+      <c r="S14" s="8" t="n">
         <v>240</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="T14" s="8" t="n">
         <v>2562</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="U14" s="8" t="n">
         <v>2520.5</v>
       </c>
     </row>
@@ -1717,13 +2048,13 @@
         <v>45870</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>175</v>
@@ -1761,13 +2092,25 @@
         <f aca="false">K15+L15+M15+N15</f>
         <v>5266</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8" t="n">
+      <c r="P15" s="10" t="n">
+        <f aca="false">IF(N(E15)&gt;0,G15/E15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10" t="n">
+        <f aca="false">IF(N(E15)&gt;0,J15/E15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <f aca="false">IF(N(E15)&gt;0,O15/E15,"")</f>
+        <v>30.0914285714286</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="8" t="n">
         <v>5266</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="U15" s="8" t="n">
         <v>5266</v>
       </c>
     </row>
@@ -1776,13 +2119,13 @@
         <v>45871</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>100</v>
@@ -1820,13 +2163,25 @@
         <f aca="false">K16+L16+M16+N16</f>
         <v>5350</v>
       </c>
-      <c r="P16" s="8" t="n">
+      <c r="P16" s="10" t="n">
+        <f aca="false">IF(N(E16)&gt;0,G16/E16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10" t="n">
+        <f aca="false">IF(N(E16)&gt;0,J16/E16,"")</f>
+        <v>45</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <f aca="false">IF(N(E16)&gt;0,O16/E16,"")</f>
+        <v>53.5</v>
+      </c>
+      <c r="S16" s="8" t="n">
         <v>1025</v>
       </c>
-      <c r="Q16" s="8" t="n">
+      <c r="T16" s="8" t="n">
         <v>7280</v>
       </c>
-      <c r="R16" s="8" t="n">
+      <c r="U16" s="8" t="n">
         <v>8348.5</v>
       </c>
     </row>
@@ -1835,13 +2190,13 @@
         <v>45878</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>60</v>
@@ -1879,13 +2234,25 @@
         <f aca="false">K17+L17+M17+N17</f>
         <v>5098.83</v>
       </c>
-      <c r="P17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8" t="n">
+      <c r="P17" s="10" t="n">
+        <f aca="false">IF(N(E17)&gt;0,G17/E17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <f aca="false">IF(N(E17)&gt;0,J17/E17,"")</f>
+        <v>15.4166666666667</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <f aca="false">IF(N(E17)&gt;0,O17/E17,"")</f>
+        <v>84.9805</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="8" t="n">
         <v>5182.08</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="U17" s="8" t="n">
         <v>5376.08</v>
       </c>
     </row>
@@ -1894,13 +2261,13 @@
         <v>45887</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>35</v>
@@ -1938,13 +2305,25 @@
         <f aca="false">K18+L18+M18+N18</f>
         <v>7681.75</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="P18" s="10" t="n">
+        <f aca="false">IF(N(E18)&gt;0,G18/E18,"")</f>
+        <v>57.8071428571429</v>
+      </c>
+      <c r="Q18" s="10" t="n">
+        <f aca="false">IF(N(E18)&gt;0,J18/E18,"")</f>
+        <v>97</v>
+      </c>
+      <c r="R18" s="10" t="n">
+        <f aca="false">IF(N(E18)&gt;0,O18/E18,"")</f>
+        <v>219.478571428571</v>
+      </c>
+      <c r="S18" s="8" t="n">
         <v>1920.44</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="T18" s="8" t="n">
         <v>10002.89</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="U18" s="8" t="n">
         <v>8065.84</v>
       </c>
     </row>
@@ -1953,13 +2332,13 @@
         <v>45891</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>125</v>
@@ -1997,13 +2376,25 @@
         <f aca="false">K19+L19+M19+N19</f>
         <v>3033</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8" t="n">
+      <c r="P19" s="10" t="n">
+        <f aca="false">IF(N(E19)&gt;0,G19/E19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <f aca="false">IF(N(E19)&gt;0,J19/E19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <f aca="false">IF(N(E19)&gt;0,O19/E19,"")</f>
+        <v>24.264</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="8" t="n">
         <v>3033</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="U19" s="8" t="n">
         <v>3033</v>
       </c>
     </row>
@@ -2012,13 +2403,13 @@
         <v>45894</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="8" t="n">
@@ -2054,10 +2445,22 @@
         <f aca="false">K20+L20+M20+N20</f>
         <v>0</v>
       </c>
-      <c r="P20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8" t="n">
+      <c r="P20" s="10" t="str">
+        <f aca="false">IF(N(E20)&gt;0,G20/E20,"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="10" t="str">
+        <f aca="false">IF(N(E20)&gt;0,J20/E20,"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="10" t="str">
+        <f aca="false">IF(N(E20)&gt;0,O20/E20,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2066,13 +2469,13 @@
         <v>45899</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>50</v>
@@ -2110,13 +2513,25 @@
         <f aca="false">K21+L21+M21+N21</f>
         <v>0</v>
       </c>
-      <c r="P21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8" t="n">
+      <c r="P21" s="10" t="n">
+        <f aca="false">IF(N(E21)&gt;0,G21/E21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <f aca="false">IF(N(E21)&gt;0,J21/E21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <f aca="false">IF(N(E21)&gt;0,O21/E21,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="8" t="n">
         <v>3235.75</v>
       </c>
     </row>
@@ -2125,13 +2540,13 @@
         <v>45905</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>140</v>
@@ -2169,13 +2584,25 @@
         <f aca="false">K22+L22+M22+N22</f>
         <v>8684.75</v>
       </c>
-      <c r="P22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8" t="n">
+      <c r="P22" s="10" t="n">
+        <f aca="false">IF(N(E22)&gt;0,G22/E22,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10" t="n">
+        <f aca="false">IF(N(E22)&gt;0,J22/E22,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <f aca="false">IF(N(E22)&gt;0,O22/E22,"")</f>
+        <v>62.0339285714286</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="8" t="n">
         <v>8684.75</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="U22" s="8" t="n">
         <v>7393.21</v>
       </c>
     </row>
@@ -2184,13 +2611,13 @@
         <v>45912</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>125</v>
@@ -2228,13 +2655,25 @@
         <f aca="false">K23+L23+M23+N23</f>
         <v>5143</v>
       </c>
-      <c r="P23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8" t="n">
+      <c r="P23" s="10" t="n">
+        <f aca="false">IF(N(E23)&gt;0,G23/E23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <f aca="false">IF(N(E23)&gt;0,J23/E23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <f aca="false">IF(N(E23)&gt;0,O23/E23,"")</f>
+        <v>41.144</v>
+      </c>
+      <c r="S23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="8" t="n">
         <v>5143</v>
       </c>
-      <c r="R23" s="8" t="n">
+      <c r="U23" s="8" t="n">
         <v>5143</v>
       </c>
     </row>
@@ -2243,13 +2682,13 @@
         <v>45916</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>75</v>
@@ -2287,13 +2726,25 @@
         <f aca="false">K24+L24+M24+N24</f>
         <v>3176</v>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="P24" s="10" t="n">
+        <f aca="false">IF(N(E24)&gt;0,G24/E24,"")</f>
+        <v>24.5333333333333</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <f aca="false">IF(N(E24)&gt;0,J24/E24,"")</f>
+        <v>17.8133333333333</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <f aca="false">IF(N(E24)&gt;0,O24/E24,"")</f>
+        <v>42.3466666666667</v>
+      </c>
+      <c r="S24" s="8" t="n">
         <v>794</v>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="T24" s="8" t="n">
         <v>4198.51</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="U24" s="8" t="n">
         <v>3369.8</v>
       </c>
     </row>
@@ -2302,13 +2753,13 @@
         <v>45920</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>150</v>
@@ -2346,13 +2797,25 @@
         <f aca="false">K25+L25+M25+N25</f>
         <v>7380</v>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="P25" s="10" t="n">
+        <f aca="false">IF(N(E25)&gt;0,G25/E25,"")</f>
+        <v>7.2</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <f aca="false">IF(N(E25)&gt;0,J25/E25,"")</f>
+        <v>40</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <f aca="false">IF(N(E25)&gt;0,O25/E25,"")</f>
+        <v>49.2</v>
+      </c>
+      <c r="S25" s="8" t="n">
         <v>1938.75</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="T25" s="8" t="n">
         <v>9851.04</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="U25" s="8" t="n">
         <v>9823.75</v>
       </c>
     </row>
@@ -2361,13 +2824,13 @@
         <v>45924</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>15</v>
@@ -2405,10 +2868,22 @@
         <f aca="false">K26+L26+M26+N26</f>
         <v>146</v>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="P26" s="10" t="n">
+        <f aca="false">IF(N(E26)&gt;0,G26/E26,"")</f>
+        <v>9.73333333333333</v>
+      </c>
+      <c r="Q26" s="10" t="n">
+        <f aca="false">IF(N(E26)&gt;0,J26/E26,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <f aca="false">IF(N(E26)&gt;0,O26/E26,"")</f>
+        <v>9.73333333333333</v>
+      </c>
+      <c r="S26" s="8" t="n">
         <v>36.5</v>
       </c>
-      <c r="Q26" s="8" t="n">
+      <c r="T26" s="8" t="n">
         <v>191.26</v>
       </c>
     </row>
@@ -2417,13 +2892,13 @@
         <v>45926</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>45</v>
@@ -2461,10 +2936,22 @@
         <f aca="false">K27+L27+M27+N27</f>
         <v>4450</v>
       </c>
-      <c r="P27" s="8" t="n">
+      <c r="P27" s="10" t="n">
+        <f aca="false">IF(N(E27)&gt;0,G27/E27,"")</f>
+        <v>43.3333333333333</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <f aca="false">IF(N(E27)&gt;0,J27/E27,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <f aca="false">IF(N(E27)&gt;0,O27/E27,"")</f>
+        <v>98.8888888888889</v>
+      </c>
+      <c r="S27" s="8" t="n">
         <v>1112.5</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="T27" s="8" t="n">
         <v>5562.5</v>
       </c>
     </row>
@@ -2473,13 +2960,13 @@
         <v>45930</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>40</v>
@@ -2517,13 +3004,25 @@
         <f aca="false">K28+L28+M28+N28</f>
         <v>447</v>
       </c>
-      <c r="P28" s="8" t="n">
+      <c r="P28" s="10" t="n">
+        <f aca="false">IF(N(E28)&gt;0,G28/E28,"")</f>
+        <v>6.25</v>
+      </c>
+      <c r="Q28" s="10" t="n">
+        <f aca="false">IF(N(E28)&gt;0,J28/E28,"")</f>
+        <v>4.925</v>
+      </c>
+      <c r="R28" s="10" t="n">
+        <f aca="false">IF(N(E28)&gt;0,O28/E28,"")</f>
+        <v>11.175</v>
+      </c>
+      <c r="S28" s="8" t="n">
         <v>111.75</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="T28" s="8" t="n">
         <v>590.1</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="U28" s="8" t="n">
         <v>516.35</v>
       </c>
     </row>
@@ -2532,13 +3031,13 @@
         <v>45932</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>50</v>
@@ -2576,13 +3075,25 @@
         <f aca="false">K29+L29+M29+N29</f>
         <v>724</v>
       </c>
-      <c r="P29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+      <c r="P29" s="10" t="n">
+        <f aca="false">IF(N(E29)&gt;0,G29/E29,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <f aca="false">IF(N(E29)&gt;0,J29/E29,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="10" t="n">
+        <f aca="false">IF(N(E29)&gt;0,O29/E29,"")</f>
+        <v>14.48</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="8" t="n">
         <v>724</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="U29" s="8" t="n">
         <v>724</v>
       </c>
     </row>
@@ -2591,13 +3102,13 @@
         <v>45933</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>140</v>
@@ -2635,13 +3146,25 @@
         <f aca="false">K30+L30+M30+N30</f>
         <v>6327</v>
       </c>
-      <c r="P30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="8" t="n">
+      <c r="P30" s="10" t="n">
+        <f aca="false">IF(N(E30)&gt;0,G30/E30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10" t="n">
+        <f aca="false">IF(N(E30)&gt;0,J30/E30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="10" t="n">
+        <f aca="false">IF(N(E30)&gt;0,O30/E30,"")</f>
+        <v>45.1928571428571</v>
+      </c>
+      <c r="S30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="8" t="n">
         <v>6327</v>
       </c>
-      <c r="R30" s="8" t="n">
+      <c r="U30" s="8" t="n">
         <v>6327</v>
       </c>
     </row>
@@ -2650,13 +3173,13 @@
         <v>45951</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>70</v>
@@ -2694,13 +3217,25 @@
         <f aca="false">K31+L31+M31+N31</f>
         <v>7866.5</v>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="P31" s="10" t="n">
+        <f aca="false">IF(N(E31)&gt;0,G31/E31,"")</f>
+        <v>48.95</v>
+      </c>
+      <c r="Q31" s="10" t="n">
+        <f aca="false">IF(N(E31)&gt;0,J31/E31,"")</f>
+        <v>59.1428571428571</v>
+      </c>
+      <c r="R31" s="10" t="n">
+        <f aca="false">IF(N(E31)&gt;0,O31/E31,"")</f>
+        <v>112.378571428571</v>
+      </c>
+      <c r="S31" s="8" t="n">
         <v>2084.95</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="T31" s="8" t="n">
         <v>10442.63</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="U31" s="8" t="n">
         <v>8172.82</v>
       </c>
     </row>
@@ -2709,13 +3244,13 @@
         <v>45951</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>65</v>
@@ -2753,10 +3288,22 @@
         <f aca="false">K32+L32+M32+N32</f>
         <v>0</v>
       </c>
-      <c r="P32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+      <c r="P32" s="10" t="n">
+        <f aca="false">IF(N(E32)&gt;0,G32/E32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="10" t="n">
+        <f aca="false">IF(N(E32)&gt;0,J32/E32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <f aca="false">IF(N(E32)&gt;0,O32/E32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2765,13 +3312,13 @@
         <v>45959</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>50</v>
@@ -2809,13 +3356,25 @@
         <f aca="false">K33+L33+M33+N33</f>
         <v>2910</v>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="P33" s="10" t="n">
+        <f aca="false">IF(N(E33)&gt;0,G33/E33,"")</f>
+        <v>18.2</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <f aca="false">IF(N(E33)&gt;0,J33/E33,"")</f>
+        <v>40</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <f aca="false">IF(N(E33)&gt;0,O33/E33,"")</f>
+        <v>58.2</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>727.5</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="T33" s="8" t="n">
         <v>3872.1</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="U33" s="8" t="n">
         <v>4490.5</v>
       </c>
     </row>
@@ -2824,13 +3383,13 @@
         <v>45981</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>11</v>
@@ -2868,13 +3427,25 @@
         <f aca="false">K34+L34+M34+N34</f>
         <v>995</v>
       </c>
-      <c r="P34" s="8" t="n">
+      <c r="P34" s="10" t="n">
+        <f aca="false">IF(N(E34)&gt;0,G34/E34,"")</f>
+        <v>45</v>
+      </c>
+      <c r="Q34" s="10" t="n">
+        <f aca="false">IF(N(E34)&gt;0,J34/E34,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="10" t="n">
+        <f aca="false">IF(N(E34)&gt;0,O34/E34,"")</f>
+        <v>90.4545454545455</v>
+      </c>
+      <c r="S34" s="8" t="n">
         <v>748.75</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="T34" s="8" t="n">
         <v>1273.45</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="U34" s="8" t="n">
         <v>1044.75</v>
       </c>
     </row>
@@ -2883,13 +3454,13 @@
         <v>45982</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>115</v>
@@ -2927,13 +3498,25 @@
         <f aca="false">K35+L35+M35+N35</f>
         <v>4622.18</v>
       </c>
-      <c r="P35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+      <c r="P35" s="10" t="n">
+        <f aca="false">IF(N(E35)&gt;0,G35/E35,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <f aca="false">IF(N(E35)&gt;0,J35/E35,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="10" t="n">
+        <f aca="false">IF(N(E35)&gt;0,O35/E35,"")</f>
+        <v>40.1928695652174</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="8" t="n">
         <v>4622.18</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="U35" s="8" t="n">
         <v>4402.45</v>
       </c>
     </row>
@@ -2942,13 +3525,13 @@
         <v>45988</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="8" t="n">
@@ -2984,10 +3567,22 @@
         <f aca="false">K36+L36+M36+N36</f>
         <v>0</v>
       </c>
-      <c r="P36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="8" t="n">
+      <c r="P36" s="10" t="str">
+        <f aca="false">IF(N(E36)&gt;0,G36/E36,"")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="10" t="str">
+        <f aca="false">IF(N(E36)&gt;0,J36/E36,"")</f>
+        <v/>
+      </c>
+      <c r="R36" s="10" t="str">
+        <f aca="false">IF(N(E36)&gt;0,O36/E36,"")</f>
+        <v/>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2996,13 +3591,13 @@
         <v>45989</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="8" t="n">
@@ -3038,10 +3633,22 @@
         <f aca="false">K37+L37+M37+N37</f>
         <v>0</v>
       </c>
-      <c r="P37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="8" t="n">
+      <c r="P37" s="10" t="str">
+        <f aca="false">IF(N(E37)&gt;0,G37/E37,"")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="10" t="str">
+        <f aca="false">IF(N(E37)&gt;0,J37/E37,"")</f>
+        <v/>
+      </c>
+      <c r="R37" s="10" t="str">
+        <f aca="false">IF(N(E37)&gt;0,O37/E37,"")</f>
+        <v/>
+      </c>
+      <c r="S37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3050,13 +3657,13 @@
         <v>45994</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>115</v>
@@ -3094,13 +3701,25 @@
         <f aca="false">K38+L38+M38+N38</f>
         <v>7335</v>
       </c>
-      <c r="P38" s="8" t="n">
+      <c r="P38" s="10" t="n">
+        <f aca="false">IF(N(E38)&gt;0,G38/E38,"")</f>
+        <v>33.9739130434783</v>
+      </c>
+      <c r="Q38" s="10" t="n">
+        <f aca="false">IF(N(E38)&gt;0,J38/E38,"")</f>
+        <v>29.8086956521739</v>
+      </c>
+      <c r="R38" s="10" t="n">
+        <f aca="false">IF(N(E38)&gt;0,O38/E38,"")</f>
+        <v>63.7826086956522</v>
+      </c>
+      <c r="S38" s="8" t="n">
         <v>1803.25</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="T38" s="8" t="n">
         <v>9547.46</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="U38" s="8" t="n">
         <v>7573.65</v>
       </c>
     </row>
@@ -3109,13 +3728,13 @@
         <v>45995</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>31</v>
@@ -3153,13 +3772,25 @@
         <f aca="false">K39+L39+M39+N39</f>
         <v>3505.5</v>
       </c>
-      <c r="P39" s="8" t="n">
+      <c r="P39" s="10" t="n">
+        <f aca="false">IF(N(E39)&gt;0,G39/E39,"")</f>
+        <v>41.0806451612903</v>
+      </c>
+      <c r="Q39" s="10" t="n">
+        <f aca="false">IF(N(E39)&gt;0,J39/E39,"")</f>
+        <v>72</v>
+      </c>
+      <c r="R39" s="10" t="n">
+        <f aca="false">IF(N(E39)&gt;0,O39/E39,"")</f>
+        <v>113.08064516129</v>
+      </c>
+      <c r="S39" s="8" t="n">
         <v>895</v>
       </c>
-      <c r="Q39" s="8" t="n">
+      <c r="T39" s="8" t="n">
         <v>4756.76</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="U39" s="8" t="n">
         <v>3759</v>
       </c>
     </row>
@@ -3168,13 +3799,13 @@
         <v>46002</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>20</v>
@@ -3212,13 +3843,25 @@
         <f aca="false">K40+L40+M40+N40</f>
         <v>2385</v>
       </c>
-      <c r="P40" s="8" t="n">
+      <c r="P40" s="10" t="n">
+        <f aca="false">IF(N(E40)&gt;0,G40/E40,"")</f>
+        <v>69.25</v>
+      </c>
+      <c r="Q40" s="10" t="n">
+        <f aca="false">IF(N(E40)&gt;0,J40/E40,"")</f>
+        <v>50</v>
+      </c>
+      <c r="R40" s="10" t="n">
+        <f aca="false">IF(N(E40)&gt;0,O40/E40,"")</f>
+        <v>119.25</v>
+      </c>
+      <c r="S40" s="8" t="n">
         <v>580.75</v>
       </c>
-      <c r="Q40" s="8" t="n">
+      <c r="T40" s="8" t="n">
         <v>2806.28</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="U40" s="8" t="n">
         <v>2178.7</v>
       </c>
     </row>
@@ -3227,13 +3870,13 @@
         <v>46005</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>175</v>
@@ -3271,13 +3914,25 @@
         <f aca="false">K41+L41+M41+N41</f>
         <v>16365</v>
       </c>
-      <c r="P41" s="8" t="n">
+      <c r="P41" s="10" t="n">
+        <f aca="false">IF(N(E41)&gt;0,G41/E41,"")</f>
+        <v>36.5142857142857</v>
+      </c>
+      <c r="Q41" s="10" t="n">
+        <f aca="false">IF(N(E41)&gt;0,J41/E41,"")</f>
+        <v>57</v>
+      </c>
+      <c r="R41" s="10" t="n">
+        <f aca="false">IF(N(E41)&gt;0,O41/E41,"")</f>
+        <v>93.5142857142857</v>
+      </c>
+      <c r="S41" s="8" t="n">
         <v>6591.25</v>
       </c>
-      <c r="Q41" s="8" t="n">
+      <c r="T41" s="8" t="n">
         <v>21737.4</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="U41" s="8" t="n">
         <v>17183.25</v>
       </c>
     </row>
@@ -3286,13 +3941,13 @@
         <v>46012</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>60</v>
@@ -3330,13 +3985,25 @@
         <f aca="false">K42+L42+M42+N42</f>
         <v>4025</v>
       </c>
-      <c r="P42" s="8" t="n">
+      <c r="P42" s="10" t="n">
+        <f aca="false">IF(N(E42)&gt;0,G42/E42,"")</f>
+        <v>50.75</v>
+      </c>
+      <c r="Q42" s="10" t="n">
+        <f aca="false">IF(N(E42)&gt;0,J42/E42,"")</f>
+        <v>16.3333333333333</v>
+      </c>
+      <c r="R42" s="10" t="n">
+        <f aca="false">IF(N(E42)&gt;0,O42/E42,"")</f>
+        <v>67.0833333333333</v>
+      </c>
+      <c r="S42" s="8" t="n">
         <v>1006.25</v>
       </c>
-      <c r="Q42" s="8" t="n">
+      <c r="T42" s="8" t="n">
         <v>5302.16</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="U42" s="8" t="n">
         <v>4718.25</v>
       </c>
     </row>
@@ -3345,13 +4012,13 @@
         <v>46031</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>24</v>
@@ -3389,13 +4056,25 @@
         <f aca="false">K43+L43+M43+N43</f>
         <v>1986</v>
       </c>
-      <c r="P43" s="8" t="n">
+      <c r="P43" s="10" t="n">
+        <f aca="false">IF(N(E43)&gt;0,G43/E43,"")</f>
+        <v>66.5416666666667</v>
+      </c>
+      <c r="Q43" s="10" t="n">
+        <f aca="false">IF(N(E43)&gt;0,J43/E43,"")</f>
+        <v>16.2083333333333</v>
+      </c>
+      <c r="R43" s="10" t="n">
+        <f aca="false">IF(N(E43)&gt;0,O43/E43,"")</f>
+        <v>82.75</v>
+      </c>
+      <c r="S43" s="8" t="n">
         <v>496.5</v>
       </c>
-      <c r="Q43" s="8" t="n">
+      <c r="T43" s="8" t="n">
         <v>2626.68</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="U43" s="8" t="n">
         <v>2112.3</v>
       </c>
     </row>
@@ -3404,13 +4083,13 @@
         <v>46032</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>24</v>
@@ -3448,13 +4127,25 @@
         <f aca="false">K44+L44+M44+N44</f>
         <v>3092</v>
       </c>
-      <c r="P44" s="8" t="n">
+      <c r="P44" s="10" t="n">
+        <f aca="false">IF(N(E44)&gt;0,G44/E44,"")</f>
+        <v>103.833333333333</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <f aca="false">IF(N(E44)&gt;0,J44/E44,"")</f>
+        <v>25</v>
+      </c>
+      <c r="R44" s="10" t="n">
+        <f aca="false">IF(N(E44)&gt;0,O44/E44,"")</f>
+        <v>128.833333333333</v>
+      </c>
+      <c r="S44" s="8" t="n">
         <v>773</v>
       </c>
-      <c r="Q44" s="8" t="n">
+      <c r="T44" s="8" t="n">
         <v>4082.92</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="U44" s="8" t="n">
         <v>3522.6</v>
       </c>
     </row>
@@ -3463,13 +4154,13 @@
         <v>46033</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>110</v>
@@ -3507,13 +4198,25 @@
         <f aca="false">K45+L45+M45+N45</f>
         <v>3902.08</v>
       </c>
-      <c r="P45" s="8" t="n">
+      <c r="P45" s="10" t="n">
+        <f aca="false">IF(N(E45)&gt;0,G45/E45,"")</f>
+        <v>19.7272727272727</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <f aca="false">IF(N(E45)&gt;0,J45/E45,"")</f>
+        <v>13.6363636363636</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <f aca="false">IF(N(E45)&gt;0,O45/E45,"")</f>
+        <v>35.4734545454545</v>
+      </c>
+      <c r="S45" s="8" t="n">
         <v>890.1</v>
       </c>
-      <c r="Q45" s="8" t="n">
+      <c r="T45" s="8" t="n">
         <v>4469.78</v>
       </c>
-      <c r="R45" s="8" t="n">
+      <c r="U45" s="8" t="n">
         <v>3486.1</v>
       </c>
     </row>
@@ -3522,13 +4225,13 @@
         <v>46038</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>60</v>
@@ -3566,13 +4269,25 @@
         <f aca="false">K46+L46+M46+N46</f>
         <v>2115</v>
       </c>
-      <c r="P46" s="8" t="n">
+      <c r="P46" s="10" t="n">
+        <f aca="false">IF(N(E46)&gt;0,G46/E46,"")</f>
+        <v>21.25</v>
+      </c>
+      <c r="Q46" s="10" t="n">
+        <f aca="false">IF(N(E46)&gt;0,J46/E46,"")</f>
+        <v>14</v>
+      </c>
+      <c r="R46" s="10" t="n">
+        <f aca="false">IF(N(E46)&gt;0,O46/E46,"")</f>
+        <v>35.25</v>
+      </c>
+      <c r="S46" s="8" t="n">
         <v>528.75</v>
       </c>
-      <c r="Q46" s="8" t="n">
+      <c r="T46" s="8" t="n">
         <v>2795.85</v>
       </c>
-      <c r="R46" s="8" t="n">
+      <c r="U46" s="8" t="n">
         <v>2262.75</v>
       </c>
     </row>
@@ -3581,13 +4296,13 @@
         <v>46040</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>34</v>
@@ -3625,13 +4340,25 @@
         <f aca="false">K47+L47+M47+N47</f>
         <v>2929</v>
       </c>
-      <c r="P47" s="8" t="n">
+      <c r="P47" s="10" t="n">
+        <f aca="false">IF(N(E47)&gt;0,G47/E47,"")</f>
+        <v>86.1470588235294</v>
+      </c>
+      <c r="Q47" s="10" t="n">
+        <f aca="false">IF(N(E47)&gt;0,J47/E47,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R47" s="10" t="n">
+        <f aca="false">IF(N(E47)&gt;0,O47/E47,"")</f>
+        <v>86.1470588235294</v>
+      </c>
+      <c r="S47" s="8" t="n">
         <v>732.25</v>
       </c>
-      <c r="Q47" s="8" t="n">
+      <c r="T47" s="8" t="n">
         <v>3836.99</v>
       </c>
-      <c r="R47" s="8" t="n">
+      <c r="U47" s="8" t="n">
         <v>3075.45</v>
       </c>
     </row>
@@ -3640,13 +4367,13 @@
         <v>46041</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>34</v>
@@ -3684,13 +4411,25 @@
         <f aca="false">K48+L48+M48+N48</f>
         <v>2338</v>
       </c>
-      <c r="P48" s="8" t="n">
+      <c r="P48" s="10" t="n">
+        <f aca="false">IF(N(E48)&gt;0,G48/E48,"")</f>
+        <v>68.7647058823529</v>
+      </c>
+      <c r="Q48" s="10" t="n">
+        <f aca="false">IF(N(E48)&gt;0,J48/E48,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R48" s="10" t="n">
+        <f aca="false">IF(N(E48)&gt;0,O48/E48,"")</f>
+        <v>68.7647058823529</v>
+      </c>
+      <c r="S48" s="8" t="n">
         <v>584.5</v>
       </c>
-      <c r="Q48" s="8" t="n">
+      <c r="T48" s="8" t="n">
         <v>3062.78</v>
       </c>
-      <c r="R48" s="8" t="n">
+      <c r="U48" s="8" t="n">
         <v>3903.9</v>
       </c>
     </row>
@@ -3699,13 +4438,13 @@
         <v>46042</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>34</v>
@@ -3743,13 +4482,25 @@
         <f aca="false">K49+L49+M49+N49</f>
         <v>3318</v>
       </c>
-      <c r="P49" s="8" t="n">
+      <c r="P49" s="10" t="n">
+        <f aca="false">IF(N(E49)&gt;0,G49/E49,"")</f>
+        <v>97.5882352941177</v>
+      </c>
+      <c r="Q49" s="10" t="n">
+        <f aca="false">IF(N(E49)&gt;0,J49/E49,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="10" t="n">
+        <f aca="false">IF(N(E49)&gt;0,O49/E49,"")</f>
+        <v>97.5882352941177</v>
+      </c>
+      <c r="S49" s="8" t="n">
         <v>829.5</v>
       </c>
-      <c r="Q49" s="8" t="n">
+      <c r="T49" s="8" t="n">
         <v>4351.08</v>
       </c>
-      <c r="R49" s="8" t="n">
+      <c r="U49" s="8" t="n">
         <v>3483.9</v>
       </c>
     </row>
@@ -3758,13 +4509,13 @@
         <v>46043</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>34</v>
@@ -3802,13 +4553,25 @@
         <f aca="false">K50+L50+M50+N50</f>
         <v>4478</v>
       </c>
-      <c r="P50" s="8" t="n">
+      <c r="P50" s="10" t="n">
+        <f aca="false">IF(N(E50)&gt;0,G50/E50,"")</f>
+        <v>131.705882352941</v>
+      </c>
+      <c r="Q50" s="10" t="n">
+        <f aca="false">IF(N(E50)&gt;0,J50/E50,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R50" s="10" t="n">
+        <f aca="false">IF(N(E50)&gt;0,O50/E50,"")</f>
+        <v>131.705882352941</v>
+      </c>
+      <c r="S50" s="8" t="n">
         <v>1119.5</v>
       </c>
-      <c r="Q50" s="8" t="n">
+      <c r="T50" s="8" t="n">
         <v>5879.61</v>
       </c>
-      <c r="R50" s="8" t="n">
+      <c r="U50" s="8" t="n">
         <v>4701.9</v>
       </c>
     </row>
@@ -3817,13 +4580,13 @@
         <v>46044</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>34</v>
@@ -3861,13 +4624,25 @@
         <f aca="false">K51+L51+M51+N51</f>
         <v>4738</v>
       </c>
-      <c r="P51" s="8" t="n">
+      <c r="P51" s="10" t="n">
+        <f aca="false">IF(N(E51)&gt;0,G51/E51,"")</f>
+        <v>139.352941176471</v>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <f aca="false">IF(N(E51)&gt;0,J51/E51,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R51" s="10" t="n">
+        <f aca="false">IF(N(E51)&gt;0,O51/E51,"")</f>
+        <v>139.352941176471</v>
+      </c>
+      <c r="S51" s="8" t="n">
         <v>1184.5</v>
       </c>
-      <c r="Q51" s="8" t="n">
+      <c r="T51" s="8" t="n">
         <v>6220.99</v>
       </c>
-      <c r="R51" s="8" t="n">
+      <c r="U51" s="8" t="n">
         <v>4974.9</v>
       </c>
     </row>
@@ -3876,13 +4651,13 @@
         <v>46045</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>20</v>
@@ -3920,13 +4695,25 @@
         <f aca="false">K52+L52+M52+N52</f>
         <v>3360</v>
       </c>
-      <c r="P52" s="8" t="n">
+      <c r="P52" s="10" t="n">
+        <f aca="false">IF(N(E52)&gt;0,G52/E52,"")</f>
+        <v>90</v>
+      </c>
+      <c r="Q52" s="10" t="n">
+        <f aca="false">IF(N(E52)&gt;0,J52/E52,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R52" s="10" t="n">
+        <f aca="false">IF(N(E52)&gt;0,O52/E52,"")</f>
+        <v>168</v>
+      </c>
+      <c r="S52" s="8" t="n">
         <v>840</v>
       </c>
-      <c r="Q52" s="8" t="n">
+      <c r="T52" s="8" t="n">
         <v>3950</v>
       </c>
-      <c r="R52" s="8" t="n">
+      <c r="U52" s="8" t="n">
         <v>6455.4</v>
       </c>
     </row>
@@ -3935,13 +4722,13 @@
         <v>46045</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>34</v>
@@ -3979,10 +4766,22 @@
         <f aca="false">K53+L53+M53+N53</f>
         <v>2788</v>
       </c>
-      <c r="P53" s="8" t="n">
+      <c r="P53" s="10" t="n">
+        <f aca="false">IF(N(E53)&gt;0,G53/E53,"")</f>
+        <v>82</v>
+      </c>
+      <c r="Q53" s="10" t="n">
+        <f aca="false">IF(N(E53)&gt;0,J53/E53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R53" s="10" t="n">
+        <f aca="false">IF(N(E53)&gt;0,O53/E53,"")</f>
+        <v>82</v>
+      </c>
+      <c r="S53" s="8" t="n">
         <v>697</v>
       </c>
-      <c r="Q53" s="8" t="n">
+      <c r="T53" s="8" t="n">
         <v>3660.64</v>
       </c>
     </row>
@@ -3991,13 +4790,13 @@
         <v>46051</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>25</v>
@@ -4035,13 +4834,25 @@
         <f aca="false">K54+L54+M54+N54</f>
         <v>1120</v>
       </c>
-      <c r="P54" s="8" t="n">
+      <c r="P54" s="10" t="n">
+        <f aca="false">IF(N(E54)&gt;0,G54/E54,"")</f>
+        <v>14</v>
+      </c>
+      <c r="Q54" s="10" t="n">
+        <f aca="false">IF(N(E54)&gt;0,J54/E54,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R54" s="10" t="n">
+        <f aca="false">IF(N(E54)&gt;0,O54/E54,"")</f>
+        <v>44.8</v>
+      </c>
+      <c r="S54" s="8" t="n">
         <v>280</v>
       </c>
-      <c r="Q54" s="8" t="n">
+      <c r="T54" s="8" t="n">
         <v>1400</v>
       </c>
-      <c r="R54" s="8" t="n">
+      <c r="U54" s="8" t="n">
         <v>1176</v>
       </c>
     </row>
@@ -4050,13 +4861,13 @@
         <v>46052</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>25</v>
@@ -4094,13 +4905,25 @@
         <f aca="false">K55+L55+M55+N55</f>
         <v>950</v>
       </c>
-      <c r="P55" s="8" t="n">
+      <c r="P55" s="10" t="n">
+        <f aca="false">IF(N(E55)&gt;0,G55/E55,"")</f>
+        <v>8</v>
+      </c>
+      <c r="Q55" s="10" t="n">
+        <f aca="false">IF(N(E55)&gt;0,J55/E55,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R55" s="10" t="n">
+        <f aca="false">IF(N(E55)&gt;0,O55/E55,"")</f>
+        <v>38</v>
+      </c>
+      <c r="S55" s="8" t="n">
         <v>230.07</v>
       </c>
-      <c r="Q55" s="8" t="n">
+      <c r="T55" s="8" t="n">
         <v>1031.43</v>
       </c>
-      <c r="R55" s="8" t="n">
+      <c r="U55" s="8" t="n">
         <v>841.43</v>
       </c>
     </row>
@@ -4109,13 +4932,13 @@
         <v>46055</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>14</v>
@@ -4153,13 +4976,25 @@
         <f aca="false">K56+L56+M56+N56</f>
         <v>2195</v>
       </c>
-      <c r="P56" s="8" t="n">
+      <c r="P56" s="10" t="n">
+        <f aca="false">IF(N(E56)&gt;0,G56/E56,"")</f>
+        <v>156.785714285714</v>
+      </c>
+      <c r="Q56" s="10" t="n">
+        <f aca="false">IF(N(E56)&gt;0,J56/E56,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R56" s="10" t="n">
+        <f aca="false">IF(N(E56)&gt;0,O56/E56,"")</f>
+        <v>156.785714285714</v>
+      </c>
+      <c r="S56" s="8" t="n">
         <v>548.75</v>
       </c>
-      <c r="Q56" s="8" t="n">
+      <c r="T56" s="8" t="n">
         <v>2875.45</v>
       </c>
-      <c r="R56" s="8" t="n">
+      <c r="U56" s="8" t="n">
         <v>2545.75</v>
       </c>
     </row>
@@ -4168,13 +5003,13 @@
         <v>46060</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>60</v>
@@ -4212,13 +5047,25 @@
         <f aca="false">K57+L57+M57+N57</f>
         <v>3095</v>
       </c>
-      <c r="P57" s="8" t="n">
+      <c r="P57" s="10" t="n">
+        <f aca="false">IF(N(E57)&gt;0,G57/E57,"")</f>
+        <v>51.5833333333333</v>
+      </c>
+      <c r="Q57" s="10" t="n">
+        <f aca="false">IF(N(E57)&gt;0,J57/E57,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R57" s="10" t="n">
+        <f aca="false">IF(N(E57)&gt;0,O57/E57,"")</f>
+        <v>51.5833333333333</v>
+      </c>
+      <c r="S57" s="8" t="n">
         <v>464.25</v>
       </c>
-      <c r="Q57" s="8" t="n">
+      <c r="T57" s="8" t="n">
         <v>3744.95</v>
       </c>
-      <c r="R57" s="8" t="n">
+      <c r="U57" s="8" t="n">
         <v>3720.25</v>
       </c>
     </row>
@@ -4227,13 +5074,13 @@
         <v>46066</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>150</v>
@@ -4271,13 +5118,25 @@
         <f aca="false">K58+L58+M58+N58</f>
         <v>8954.8</v>
       </c>
-      <c r="P58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="8" t="n">
+      <c r="P58" s="10" t="n">
+        <f aca="false">IF(N(E58)&gt;0,G58/E58,"")</f>
+        <v>46.412</v>
+      </c>
+      <c r="Q58" s="10" t="n">
+        <f aca="false">IF(N(E58)&gt;0,J58/E58,"")</f>
+        <v>13.2866666666667</v>
+      </c>
+      <c r="R58" s="10" t="n">
+        <f aca="false">IF(N(E58)&gt;0,O58/E58,"")</f>
+        <v>59.6986666666667</v>
+      </c>
+      <c r="S58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="8" t="n">
         <v>8954.8</v>
       </c>
-      <c r="R58" s="8" t="n">
+      <c r="U58" s="8" t="n">
         <v>1993</v>
       </c>
     </row>
@@ -4286,13 +5145,13 @@
         <v>46081</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>32</v>
@@ -4330,13 +5189,25 @@
         <f aca="false">K59+L59+M59+N59</f>
         <v>3080</v>
       </c>
-      <c r="P59" s="8" t="n">
+      <c r="P59" s="10" t="n">
+        <f aca="false">IF(N(E59)&gt;0,G59/E59,"")</f>
+        <v>21.25</v>
+      </c>
+      <c r="Q59" s="10" t="n">
+        <f aca="false">IF(N(E59)&gt;0,J59/E59,"")</f>
+        <v>75</v>
+      </c>
+      <c r="R59" s="10" t="n">
+        <f aca="false">IF(N(E59)&gt;0,O59/E59,"")</f>
+        <v>96.25</v>
+      </c>
+      <c r="S59" s="8" t="n">
         <v>154</v>
       </c>
-      <c r="Q59" s="8" t="n">
+      <c r="T59" s="8" t="n">
         <v>3490.8</v>
       </c>
-      <c r="R59" s="8" t="n">
+      <c r="U59" s="8" t="n">
         <v>3234</v>
       </c>
     </row>
@@ -4345,13 +5216,13 @@
         <v>46082</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E60" s="7" t="n">
         <v>125</v>
@@ -4389,13 +5260,25 @@
         <f aca="false">K60+L60+M60+N60</f>
         <v>3414</v>
       </c>
-      <c r="P60" s="8" t="n">
+      <c r="P60" s="10" t="n">
+        <f aca="false">IF(N(E60)&gt;0,G60/E60,"")</f>
+        <v>18.44</v>
+      </c>
+      <c r="Q60" s="10" t="n">
+        <f aca="false">IF(N(E60)&gt;0,J60/E60,"")</f>
+        <v>8.872</v>
+      </c>
+      <c r="R60" s="10" t="n">
+        <f aca="false">IF(N(E60)&gt;0,O60/E60,"")</f>
+        <v>27.312</v>
+      </c>
+      <c r="S60" s="8" t="n">
         <v>838</v>
       </c>
-      <c r="Q60" s="8" t="n">
+      <c r="T60" s="8" t="n">
         <v>4145.7</v>
       </c>
-      <c r="R60" s="8" t="n">
+      <c r="U60" s="8" t="n">
         <v>4784.6</v>
       </c>
     </row>
@@ -4404,13 +5287,13 @@
         <v>46085</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E61" s="7" t="n">
         <v>6</v>
@@ -4448,13 +5331,25 @@
         <f aca="false">K61+L61+M61+N61</f>
         <v>800</v>
       </c>
-      <c r="P61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="8" t="n">
+      <c r="P61" s="10" t="n">
+        <f aca="false">IF(N(E61)&gt;0,G61/E61,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="10" t="n">
+        <f aca="false">IF(N(E61)&gt;0,J61/E61,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R61" s="10" t="n">
+        <f aca="false">IF(N(E61)&gt;0,O61/E61,"")</f>
+        <v>133.333333333333</v>
+      </c>
+      <c r="S61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="R61" s="8" t="n">
+      <c r="U61" s="8" t="n">
         <v>800</v>
       </c>
     </row>
@@ -4463,13 +5358,13 @@
         <v>46086</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>50</v>
@@ -4507,13 +5402,25 @@
         <f aca="false">K62+L62+M62+N62</f>
         <v>631</v>
       </c>
-      <c r="P62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="8" t="n">
+      <c r="P62" s="10" t="n">
+        <f aca="false">IF(N(E62)&gt;0,G62/E62,"")</f>
+        <v>12.62</v>
+      </c>
+      <c r="Q62" s="10" t="n">
+        <f aca="false">IF(N(E62)&gt;0,J62/E62,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R62" s="10" t="n">
+        <f aca="false">IF(N(E62)&gt;0,O62/E62,"")</f>
+        <v>12.62</v>
+      </c>
+      <c r="S62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="8" t="n">
         <v>631</v>
       </c>
-      <c r="R62" s="8" t="n">
+      <c r="U62" s="8" t="n">
         <v>631</v>
       </c>
     </row>
@@ -4522,13 +5429,13 @@
         <v>46088</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>112</v>
@@ -4566,13 +5473,25 @@
         <f aca="false">K63+L63+M63+N63</f>
         <v>9999</v>
       </c>
-      <c r="P63" s="8" t="n">
+      <c r="P63" s="10" t="n">
+        <f aca="false">IF(N(E63)&gt;0,G63/E63,"")</f>
+        <v>67.5446428571429</v>
+      </c>
+      <c r="Q63" s="10" t="n">
+        <f aca="false">IF(N(E63)&gt;0,J63/E63,"")</f>
+        <v>21.7321428571429</v>
+      </c>
+      <c r="R63" s="10" t="n">
+        <f aca="false">IF(N(E63)&gt;0,O63/E63,"")</f>
+        <v>89.2767857142857</v>
+      </c>
+      <c r="S63" s="8" t="n">
         <v>2499.75</v>
       </c>
-      <c r="Q63" s="8" t="n">
+      <c r="T63" s="8" t="n">
         <v>13201.71</v>
       </c>
-      <c r="R63" s="8" t="n">
+      <c r="U63" s="8" t="n">
         <v>10498.95</v>
       </c>
     </row>
@@ -4581,13 +5500,13 @@
         <v>46091</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>24</v>
@@ -4625,13 +5544,25 @@
         <f aca="false">K64+L64+M64+N64</f>
         <v>1274</v>
       </c>
-      <c r="P64" s="8" t="n">
+      <c r="P64" s="10" t="n">
+        <f aca="false">IF(N(E64)&gt;0,G64/E64,"")</f>
+        <v>53.0833333333333</v>
+      </c>
+      <c r="Q64" s="10" t="n">
+        <f aca="false">IF(N(E64)&gt;0,J64/E64,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R64" s="10" t="n">
+        <f aca="false">IF(N(E64)&gt;0,O64/E64,"")</f>
+        <v>53.0833333333333</v>
+      </c>
+      <c r="S64" s="8" t="n">
         <v>302</v>
       </c>
-      <c r="Q64" s="8" t="n">
+      <c r="T64" s="8" t="n">
         <v>1652.44</v>
       </c>
-      <c r="R64" s="8" t="n">
+      <c r="U64" s="8" t="n">
         <v>1288.9</v>
       </c>
     </row>
@@ -4640,13 +5571,13 @@
         <v>46092</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E65" s="7" t="n">
         <v>50</v>
@@ -4684,13 +5615,25 @@
         <f aca="false">K65+L65+M65+N65</f>
         <v>543</v>
       </c>
-      <c r="P65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="8" t="n">
+      <c r="P65" s="10" t="n">
+        <f aca="false">IF(N(E65)&gt;0,G65/E65,"")</f>
+        <v>10.86</v>
+      </c>
+      <c r="Q65" s="10" t="n">
+        <f aca="false">IF(N(E65)&gt;0,J65/E65,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R65" s="10" t="n">
+        <f aca="false">IF(N(E65)&gt;0,O65/E65,"")</f>
+        <v>10.86</v>
+      </c>
+      <c r="S65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="8" t="n">
         <v>543</v>
       </c>
-      <c r="R65" s="8" t="n">
+      <c r="U65" s="8" t="n">
         <v>408</v>
       </c>
     </row>
@@ -4699,13 +5642,13 @@
         <v>46095</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E66" s="7" t="n">
         <v>55</v>
@@ -4743,13 +5686,25 @@
         <f aca="false">K66+L66+M66+N66</f>
         <v>4665.5</v>
       </c>
-      <c r="P66" s="8" t="n">
+      <c r="P66" s="10" t="n">
+        <f aca="false">IF(N(E66)&gt;0,G66/E66,"")</f>
+        <v>77.0454545454546</v>
+      </c>
+      <c r="Q66" s="10" t="n">
+        <f aca="false">IF(N(E66)&gt;0,J66/E66,"")</f>
+        <v>7.78181818181818</v>
+      </c>
+      <c r="R66" s="10" t="n">
+        <f aca="false">IF(N(E66)&gt;0,O66/E66,"")</f>
+        <v>84.8272727272727</v>
+      </c>
+      <c r="S66" s="8" t="n">
         <v>880.62</v>
       </c>
-      <c r="Q66" s="8" t="n">
+      <c r="T66" s="8" t="n">
         <v>5795.06</v>
       </c>
-      <c r="R66" s="8" t="n">
+      <c r="U66" s="8" t="n">
         <v>4138.62</v>
       </c>
     </row>
@@ -4758,13 +5713,13 @@
         <v>46096</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>130</v>
@@ -4802,13 +5757,25 @@
         <f aca="false">K67+L67+M67+N67</f>
         <v>7337.97</v>
       </c>
-      <c r="P67" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="8" t="n">
+      <c r="P67" s="10" t="n">
+        <f aca="false">IF(N(E67)&gt;0,G67/E67,"")</f>
+        <v>41.2536153846154</v>
+      </c>
+      <c r="Q67" s="10" t="n">
+        <f aca="false">IF(N(E67)&gt;0,J67/E67,"")</f>
+        <v>15.1923076923077</v>
+      </c>
+      <c r="R67" s="10" t="n">
+        <f aca="false">IF(N(E67)&gt;0,O67/E67,"")</f>
+        <v>56.4459230769231</v>
+      </c>
+      <c r="S67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="8" t="n">
         <v>7337.97</v>
       </c>
-      <c r="R67" s="8" t="n">
+      <c r="U67" s="8" t="n">
         <v>7234.97</v>
       </c>
     </row>
@@ -4817,13 +5784,13 @@
         <v>46100</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>100</v>
@@ -4861,13 +5828,25 @@
         <f aca="false">K68+L68+M68+N68</f>
         <v>2198.35</v>
       </c>
-      <c r="P68" s="8" t="n">
+      <c r="P68" s="10" t="n">
+        <f aca="false">IF(N(E68)&gt;0,G68/E68,"")</f>
+        <v>11.9</v>
+      </c>
+      <c r="Q68" s="10" t="n">
+        <f aca="false">IF(N(E68)&gt;0,J68/E68,"")</f>
+        <v>10.0835</v>
+      </c>
+      <c r="R68" s="10" t="n">
+        <f aca="false">IF(N(E68)&gt;0,O68/E68,"")</f>
+        <v>21.9835</v>
+      </c>
+      <c r="S68" s="8" t="n">
         <v>499.17</v>
       </c>
-      <c r="Q68" s="8" t="n">
+      <c r="T68" s="8" t="n">
         <v>2768.92</v>
       </c>
-      <c r="R68" s="8" t="n">
+      <c r="U68" s="8" t="n">
         <v>2248.75</v>
       </c>
     </row>
@@ -4876,13 +5855,13 @@
         <v>46101</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>30</v>
@@ -4920,13 +5899,25 @@
         <f aca="false">K69+L69+M69+N69</f>
         <v>2495</v>
       </c>
-      <c r="P69" s="8" t="n">
+      <c r="P69" s="10" t="n">
+        <f aca="false">IF(N(E69)&gt;0,G69/E69,"")</f>
+        <v>34.8333333333333</v>
+      </c>
+      <c r="Q69" s="10" t="n">
+        <f aca="false">IF(N(E69)&gt;0,J69/E69,"")</f>
+        <v>40</v>
+      </c>
+      <c r="R69" s="10" t="n">
+        <f aca="false">IF(N(E69)&gt;0,O69/E69,"")</f>
+        <v>83.1666666666667</v>
+      </c>
+      <c r="S69" s="8" t="n">
         <v>623.75</v>
       </c>
-      <c r="Q69" s="8" t="n">
+      <c r="T69" s="8" t="n">
         <v>3289.45</v>
       </c>
-      <c r="R69" s="8" t="n">
+      <c r="U69" s="8" t="n">
         <v>2969.75</v>
       </c>
     </row>
@@ -4935,13 +5926,13 @@
         <v>46102</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>16</v>
@@ -4979,13 +5970,25 @@
         <f aca="false">K70+L70+M70+N70</f>
         <v>2120</v>
       </c>
-      <c r="P70" s="8" t="n">
+      <c r="P70" s="10" t="n">
+        <f aca="false">IF(N(E70)&gt;0,G70/E70,"")</f>
+        <v>132.5</v>
+      </c>
+      <c r="Q70" s="10" t="n">
+        <f aca="false">IF(N(E70)&gt;0,J70/E70,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R70" s="10" t="n">
+        <f aca="false">IF(N(E70)&gt;0,O70/E70,"")</f>
+        <v>132.5</v>
+      </c>
+      <c r="S70" s="8" t="n">
         <v>530</v>
       </c>
-      <c r="Q70" s="8" t="n">
+      <c r="T70" s="8" t="n">
         <v>2777.2</v>
       </c>
-      <c r="R70" s="8" t="n">
+      <c r="U70" s="8" t="n">
         <v>4287</v>
       </c>
     </row>
@@ -4994,13 +5997,13 @@
         <v>46102</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>68</v>
@@ -5038,10 +6041,22 @@
         <f aca="false">K71+L71+M71+N71</f>
         <v>3843</v>
       </c>
-      <c r="P71" s="8" t="n">
+      <c r="P71" s="10" t="n">
+        <f aca="false">IF(N(E71)&gt;0,G71/E71,"")</f>
+        <v>29.4411764705882</v>
+      </c>
+      <c r="Q71" s="10" t="n">
+        <f aca="false">IF(N(E71)&gt;0,J71/E71,"")</f>
+        <v>27.0735294117647</v>
+      </c>
+      <c r="R71" s="10" t="n">
+        <f aca="false">IF(N(E71)&gt;0,O71/E71,"")</f>
+        <v>56.5147058823529</v>
+      </c>
+      <c r="S71" s="8" t="n">
         <v>960.75</v>
       </c>
-      <c r="Q71" s="8" t="n">
+      <c r="T71" s="8" t="n">
         <v>5087.52</v>
       </c>
     </row>
@@ -5050,13 +6065,13 @@
         <v>46109</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E72" s="7" t="n">
         <v>30</v>
@@ -5094,10 +6109,22 @@
         <f aca="false">K72+L72+M72+N72</f>
         <v>0</v>
       </c>
-      <c r="P72" s="8" t="n">
+      <c r="P72" s="10" t="n">
+        <f aca="false">IF(N(E72)&gt;0,G72/E72,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q72" s="10" t="n">
+        <f aca="false">IF(N(E72)&gt;0,J72/E72,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R72" s="10" t="n">
+        <f aca="false">IF(N(E72)&gt;0,O72/E72,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S72" s="8" t="n">
         <v>583.33</v>
       </c>
-      <c r="Q72" s="8" t="n">
+      <c r="T72" s="8" t="n">
         <v>500</v>
       </c>
     </row>
@@ -5106,13 +6133,13 @@
         <v>46122</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>30</v>
@@ -5150,13 +6177,25 @@
         <f aca="false">K73+L73+M73+N73</f>
         <v>2457.58</v>
       </c>
-      <c r="P73" s="8" t="n">
+      <c r="P73" s="10" t="n">
+        <f aca="false">IF(N(E73)&gt;0,G73/E73,"")</f>
+        <v>30</v>
+      </c>
+      <c r="Q73" s="10" t="n">
+        <f aca="false">IF(N(E73)&gt;0,J73/E73,"")</f>
+        <v>16.9193333333333</v>
+      </c>
+      <c r="R73" s="10" t="n">
+        <f aca="false">IF(N(E73)&gt;0,O73/E73,"")</f>
+        <v>81.9193333333333</v>
+      </c>
+      <c r="S73" s="8" t="n">
         <v>517.5</v>
       </c>
-      <c r="Q73" s="8" t="n">
+      <c r="T73" s="8" t="n">
         <v>3029.08</v>
       </c>
-      <c r="R73" s="8" t="n">
+      <c r="U73" s="8" t="n">
         <v>2703.5</v>
       </c>
     </row>
@@ -5165,13 +6204,13 @@
         <v>46124</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>30</v>
@@ -5209,13 +6248,25 @@
         <f aca="false">K74+L74+M74+N74</f>
         <v>2150</v>
       </c>
-      <c r="P74" s="8" t="n">
+      <c r="P74" s="10" t="n">
+        <f aca="false">IF(N(E74)&gt;0,G74/E74,"")</f>
+        <v>45</v>
+      </c>
+      <c r="Q74" s="10" t="n">
+        <f aca="false">IF(N(E74)&gt;0,J74/E74,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R74" s="10" t="n">
+        <f aca="false">IF(N(E74)&gt;0,O74/E74,"")</f>
+        <v>71.6666666666667</v>
+      </c>
+      <c r="S74" s="8" t="n">
         <v>607.5</v>
       </c>
-      <c r="Q74" s="8" t="n">
+      <c r="T74" s="8" t="n">
         <v>2838.5</v>
       </c>
-      <c r="R74" s="8" t="n">
+      <c r="U74" s="8" t="n">
         <v>2487.5</v>
       </c>
     </row>
@@ -5224,13 +6275,13 @@
         <v>46136</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>30</v>
@@ -5268,13 +6319,25 @@
         <f aca="false">K75+L75+M75+N75</f>
         <v>583</v>
       </c>
-      <c r="P75" s="8" t="n">
+      <c r="P75" s="10" t="n">
+        <f aca="false">IF(N(E75)&gt;0,G75/E75,"")</f>
+        <v>14</v>
+      </c>
+      <c r="Q75" s="10" t="n">
+        <f aca="false">IF(N(E75)&gt;0,J75/E75,"")</f>
+        <v>5.43333333333333</v>
+      </c>
+      <c r="R75" s="10" t="n">
+        <f aca="false">IF(N(E75)&gt;0,O75/E75,"")</f>
+        <v>19.4333333333333</v>
+      </c>
+      <c r="S75" s="8" t="n">
         <v>281.54</v>
       </c>
-      <c r="Q75" s="8" t="n">
+      <c r="T75" s="8" t="n">
         <v>839.73</v>
       </c>
-      <c r="R75" s="8" t="n">
+      <c r="U75" s="8" t="n">
         <v>1013</v>
       </c>
     </row>
@@ -5283,13 +6346,13 @@
         <v>46137</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E76" s="7" t="n">
         <v>68</v>
@@ -5327,13 +6390,25 @@
         <f aca="false">K76+L76+M76+N76</f>
         <v>3997</v>
       </c>
-      <c r="P76" s="8" t="n">
+      <c r="P76" s="10" t="n">
+        <f aca="false">IF(N(E76)&gt;0,G76/E76,"")</f>
+        <v>29.0441176470588</v>
+      </c>
+      <c r="Q76" s="10" t="n">
+        <f aca="false">IF(N(E76)&gt;0,J76/E76,"")</f>
+        <v>29.7352941176471</v>
+      </c>
+      <c r="R76" s="10" t="n">
+        <f aca="false">IF(N(E76)&gt;0,O76/E76,"")</f>
+        <v>58.7794117647059</v>
+      </c>
+      <c r="S76" s="8" t="n">
         <v>3078.75</v>
       </c>
-      <c r="Q76" s="8" t="n">
+      <c r="T76" s="8" t="n">
         <v>6965.73</v>
       </c>
-      <c r="R76" s="8" t="n">
+      <c r="U76" s="8" t="n">
         <v>6322.75</v>
       </c>
     </row>
@@ -5342,13 +6417,13 @@
         <v>46147</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E77" s="7" t="n">
         <v>60</v>
@@ -5386,13 +6461,25 @@
         <f aca="false">K77+L77+M77+N77</f>
         <v>3900</v>
       </c>
-      <c r="P77" s="8" t="n">
+      <c r="P77" s="10" t="n">
+        <f aca="false">IF(N(E77)&gt;0,G77/E77,"")</f>
+        <v>27.8333333333333</v>
+      </c>
+      <c r="Q77" s="10" t="n">
+        <f aca="false">IF(N(E77)&gt;0,J77/E77,"")</f>
+        <v>33</v>
+      </c>
+      <c r="R77" s="10" t="n">
+        <f aca="false">IF(N(E77)&gt;0,O77/E77,"")</f>
+        <v>65</v>
+      </c>
+      <c r="S77" s="8" t="n">
         <v>1762.5</v>
       </c>
-      <c r="Q77" s="8" t="n">
+      <c r="T77" s="8" t="n">
         <v>5840.9</v>
       </c>
-      <c r="R77" s="8" t="n">
+      <c r="U77" s="8" t="n">
         <v>5312.5</v>
       </c>
     </row>
@@ -5401,13 +6488,13 @@
         <v>46149</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E78" s="7" t="n">
         <v>20</v>
@@ -5445,13 +6532,25 @@
         <f aca="false">K78+L78+M78+N78</f>
         <v>1720</v>
       </c>
-      <c r="P78" s="8" t="n">
+      <c r="P78" s="10" t="n">
+        <f aca="false">IF(N(E78)&gt;0,G78/E78,"")</f>
+        <v>60.25</v>
+      </c>
+      <c r="Q78" s="10" t="n">
+        <f aca="false">IF(N(E78)&gt;0,J78/E78,"")</f>
+        <v>13.25</v>
+      </c>
+      <c r="R78" s="10" t="n">
+        <f aca="false">IF(N(E78)&gt;0,O78/E78,"")</f>
+        <v>86</v>
+      </c>
+      <c r="S78" s="8" t="n">
         <v>748.25</v>
       </c>
-      <c r="Q78" s="8" t="n">
+      <c r="T78" s="8" t="n">
         <v>2564.4</v>
       </c>
-      <c r="R78" s="8" t="n">
+      <c r="U78" s="8" t="n">
         <v>1771.25</v>
       </c>
     </row>
@@ -5460,13 +6559,13 @@
         <v>46154</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>55</v>
@@ -5504,13 +6603,25 @@
         <f aca="false">K79+L79+M79+N79</f>
         <v>2065</v>
       </c>
-      <c r="P79" s="8" t="n">
+      <c r="P79" s="10" t="n">
+        <f aca="false">IF(N(E79)&gt;0,G79/E79,"")</f>
+        <v>10.2727272727273</v>
+      </c>
+      <c r="Q79" s="10" t="n">
+        <f aca="false">IF(N(E79)&gt;0,J79/E79,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R79" s="10" t="n">
+        <f aca="false">IF(N(E79)&gt;0,O79/E79,"")</f>
+        <v>37.5454545454546</v>
+      </c>
+      <c r="S79" s="8" t="n">
         <v>501.25</v>
       </c>
-      <c r="Q79" s="8" t="n">
+      <c r="T79" s="8" t="n">
         <v>2266.26</v>
       </c>
-      <c r="R79" s="8" t="n">
+      <c r="U79" s="8" t="n">
         <v>2539.25</v>
       </c>
     </row>
@@ -5519,13 +6630,13 @@
         <v>46155</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>45</v>
@@ -5563,13 +6674,25 @@
         <f aca="false">K80+L80+M80+N80</f>
         <v>4419</v>
       </c>
-      <c r="P80" s="8" t="n">
+      <c r="P80" s="10" t="n">
+        <f aca="false">IF(N(E80)&gt;0,G80/E80,"")</f>
+        <v>37.0888888888889</v>
+      </c>
+      <c r="Q80" s="10" t="n">
+        <f aca="false">IF(N(E80)&gt;0,J80/E80,"")</f>
+        <v>50</v>
+      </c>
+      <c r="R80" s="10" t="n">
+        <f aca="false">IF(N(E80)&gt;0,O80/E80,"")</f>
+        <v>98.2</v>
+      </c>
+      <c r="S80" s="8" t="n">
         <v>1979.75</v>
       </c>
-      <c r="Q80" s="8" t="n">
+      <c r="T80" s="8" t="n">
         <v>6633.89</v>
       </c>
-      <c r="R80" s="8" t="n">
+      <c r="U80" s="8" t="n">
         <v>6398.75</v>
       </c>
     </row>
@@ -5578,13 +6701,13 @@
         <v>46156</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>11</v>
@@ -5622,13 +6745,25 @@
         <f aca="false">K81+L81+M81+N81</f>
         <v>1895</v>
       </c>
-      <c r="P81" s="8" t="n">
+      <c r="P81" s="10" t="n">
+        <f aca="false">IF(N(E81)&gt;0,G81/E81,"")</f>
+        <v>117.727272727273</v>
+      </c>
+      <c r="Q81" s="10" t="n">
+        <f aca="false">IF(N(E81)&gt;0,J81/E81,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R81" s="10" t="n">
+        <f aca="false">IF(N(E81)&gt;0,O81/E81,"")</f>
+        <v>172.272727272727</v>
+      </c>
+      <c r="S81" s="8" t="n">
         <v>1723.75</v>
       </c>
-      <c r="Q81" s="8" t="n">
+      <c r="T81" s="8" t="n">
         <v>3696.45</v>
       </c>
-      <c r="R81" s="8" t="n">
+      <c r="U81" s="8" t="n">
         <v>3618.75</v>
       </c>
     </row>
@@ -5637,13 +6772,13 @@
         <v>46157</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>11</v>
@@ -5681,13 +6816,25 @@
         <f aca="false">K82+L82+M82+N82</f>
         <v>2297</v>
       </c>
-      <c r="P82" s="8" t="n">
+      <c r="P82" s="10" t="n">
+        <f aca="false">IF(N(E82)&gt;0,G82/E82,"")</f>
+        <v>154.272727272727</v>
+      </c>
+      <c r="Q82" s="10" t="n">
+        <f aca="false">IF(N(E82)&gt;0,J82/E82,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R82" s="10" t="n">
+        <f aca="false">IF(N(E82)&gt;0,O82/E82,"")</f>
+        <v>208.818181818182</v>
+      </c>
+      <c r="S82" s="8" t="n">
         <v>1824.25</v>
       </c>
-      <c r="Q82" s="8" t="n">
+      <c r="T82" s="8" t="n">
         <v>4223.07</v>
       </c>
-      <c r="R82" s="8" t="n">
+      <c r="U82" s="8" t="n">
         <v>4146.25</v>
       </c>
     </row>
@@ -5696,13 +6843,13 @@
         <v>46162</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>75</v>
@@ -5740,13 +6887,25 @@
         <f aca="false">K83+L83+M83+N83</f>
         <v>6864</v>
       </c>
-      <c r="P83" s="8" t="n">
+      <c r="P83" s="10" t="n">
+        <f aca="false">IF(N(E83)&gt;0,G83/E83,"")</f>
+        <v>26.1866666666667</v>
+      </c>
+      <c r="Q83" s="10" t="n">
+        <f aca="false">IF(N(E83)&gt;0,J83/E83,"")</f>
+        <v>62</v>
+      </c>
+      <c r="R83" s="10" t="n">
+        <f aca="false">IF(N(E83)&gt;0,O83/E83,"")</f>
+        <v>91.52</v>
+      </c>
+      <c r="S83" s="8" t="n">
         <v>3652.4</v>
       </c>
-      <c r="Q83" s="8" t="n">
+      <c r="T83" s="8" t="n">
         <v>11052.74</v>
       </c>
-      <c r="R83" s="8" t="n">
+      <c r="U83" s="8" t="n">
         <v>9830</v>
       </c>
     </row>
@@ -5755,13 +6914,13 @@
         <v>46163</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>50</v>
@@ -5799,13 +6958,25 @@
         <f aca="false">K84+L84+M84+N84</f>
         <v>1489</v>
       </c>
-      <c r="P84" s="8" t="n">
+      <c r="P84" s="10" t="n">
+        <f aca="false">IF(N(E84)&gt;0,G84/E84,"")</f>
+        <v>13</v>
+      </c>
+      <c r="Q84" s="10" t="n">
+        <f aca="false">IF(N(E84)&gt;0,J84/E84,"")</f>
+        <v>11.78</v>
+      </c>
+      <c r="R84" s="10" t="n">
+        <f aca="false">IF(N(E84)&gt;0,O84/E84,"")</f>
+        <v>29.78</v>
+      </c>
+      <c r="S84" s="8" t="n">
         <v>1800.6</v>
       </c>
-      <c r="Q84" s="8" t="n">
+      <c r="T84" s="8" t="n">
         <v>3341.89</v>
       </c>
-      <c r="R84" s="8" t="n">
+      <c r="U84" s="8" t="n">
         <v>2756</v>
       </c>
     </row>
@@ -5814,13 +6985,13 @@
         <v>46172</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>100</v>
@@ -5858,13 +7029,25 @@
         <f aca="false">K85+L85+M85+N85</f>
         <v>1965</v>
       </c>
-      <c r="P85" s="8" t="n">
+      <c r="P85" s="10" t="n">
+        <f aca="false">IF(N(E85)&gt;0,G85/E85,"")</f>
+        <v>14.65</v>
+      </c>
+      <c r="Q85" s="10" t="n">
+        <f aca="false">IF(N(E85)&gt;0,J85/E85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R85" s="10" t="n">
+        <f aca="false">IF(N(E85)&gt;0,O85/E85,"")</f>
+        <v>19.65</v>
+      </c>
+      <c r="S85" s="8" t="n">
         <v>1691.25</v>
       </c>
-      <c r="Q85" s="8" t="n">
+      <c r="T85" s="8" t="n">
         <v>3744.15</v>
       </c>
-      <c r="R85" s="8" t="n">
+      <c r="U85" s="8" t="n">
         <v>602</v>
       </c>
     </row>
@@ -5873,13 +7056,13 @@
         <v>46173</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>50</v>
@@ -5917,13 +7100,25 @@
         <f aca="false">K86+L86+M86+N86</f>
         <v>1295</v>
       </c>
-      <c r="P86" s="8" t="n">
+      <c r="P86" s="10" t="n">
+        <f aca="false">IF(N(E86)&gt;0,G86/E86,"")</f>
+        <v>25.9</v>
+      </c>
+      <c r="Q86" s="10" t="n">
+        <f aca="false">IF(N(E86)&gt;0,J86/E86,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R86" s="10" t="n">
+        <f aca="false">IF(N(E86)&gt;0,O86/E86,"")</f>
+        <v>25.9</v>
+      </c>
+      <c r="S86" s="8" t="n">
         <v>3198.75</v>
       </c>
-      <c r="Q86" s="8" t="n">
+      <c r="T86" s="8" t="n">
         <v>3571.45</v>
       </c>
-      <c r="R86" s="8" t="n">
+      <c r="U86" s="8" t="n">
         <v>3493.75</v>
       </c>
     </row>
@@ -5932,13 +7127,13 @@
         <v>46175</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>30</v>
@@ -5976,13 +7171,25 @@
         <f aca="false">K87+L87+M87+N87</f>
         <v>1744</v>
       </c>
-      <c r="P87" s="8" t="n">
+      <c r="P87" s="10" t="n">
+        <f aca="false">IF(N(E87)&gt;0,G87/E87,"")</f>
+        <v>33.1333333333333</v>
+      </c>
+      <c r="Q87" s="10" t="n">
+        <f aca="false">IF(N(E87)&gt;0,J87/E87,"")</f>
+        <v>25</v>
+      </c>
+      <c r="R87" s="10" t="n">
+        <f aca="false">IF(N(E87)&gt;0,O87/E87,"")</f>
+        <v>58.1333333333333</v>
+      </c>
+      <c r="S87" s="8" t="n">
         <v>540.64</v>
       </c>
-      <c r="Q87" s="8" t="n">
+      <c r="T87" s="8" t="n">
         <v>2284.64</v>
       </c>
-      <c r="R87" s="8" t="n">
+      <c r="U87" s="8" t="n">
         <v>5523.45</v>
       </c>
     </row>
@@ -5991,13 +7198,13 @@
         <v>46179</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>30</v>
@@ -6035,13 +7242,25 @@
         <f aca="false">K88+L88+M88+N88</f>
         <v>1728</v>
       </c>
-      <c r="P88" s="8" t="n">
+      <c r="P88" s="10" t="n">
+        <f aca="false">IF(N(E88)&gt;0,G88/E88,"")</f>
+        <v>9.4</v>
+      </c>
+      <c r="Q88" s="10" t="n">
+        <f aca="false">IF(N(E88)&gt;0,J88/E88,"")</f>
+        <v>39.8666666666667</v>
+      </c>
+      <c r="R88" s="10" t="n">
+        <f aca="false">IF(N(E88)&gt;0,O88/E88,"")</f>
+        <v>57.6</v>
+      </c>
+      <c r="S88" s="8" t="n">
         <v>946.75</v>
       </c>
-      <c r="Q88" s="8" t="n">
+      <c r="T88" s="8" t="n">
         <v>3562.33</v>
       </c>
-      <c r="R88" s="8" t="n">
+      <c r="U88" s="8" t="n">
         <v>3437.77</v>
       </c>
     </row>
@@ -6050,13 +7269,13 @@
         <v>46180</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>57</v>
@@ -6094,13 +7313,25 @@
         <f aca="false">K89+L89+M89+N89</f>
         <v>1000</v>
       </c>
-      <c r="P89" s="8" t="n">
+      <c r="P89" s="10" t="n">
+        <f aca="false">IF(N(E89)&gt;0,G89/E89,"")</f>
+        <v>8.7719298245614</v>
+      </c>
+      <c r="Q89" s="10" t="n">
+        <f aca="false">IF(N(E89)&gt;0,J89/E89,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R89" s="10" t="n">
+        <f aca="false">IF(N(E89)&gt;0,O89/E89,"")</f>
+        <v>17.5438596491228</v>
+      </c>
+      <c r="S89" s="8" t="n">
         <v>2630</v>
       </c>
-      <c r="Q89" s="8" t="n">
+      <c r="T89" s="8" t="n">
         <v>3630</v>
       </c>
-      <c r="R89" s="8" t="n">
+      <c r="U89" s="8" t="n">
         <v>4956</v>
       </c>
     </row>
@@ -6109,13 +7340,13 @@
         <v>46185</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E90" s="7" t="n">
         <v>75</v>
@@ -6153,13 +7384,25 @@
         <f aca="false">K90+L90+M90+N90</f>
         <v>750</v>
       </c>
-      <c r="P90" s="8" t="n">
+      <c r="P90" s="10" t="n">
+        <f aca="false">IF(N(E90)&gt;0,G90/E90,"")</f>
+        <v>6.66666666666667</v>
+      </c>
+      <c r="Q90" s="10" t="n">
+        <f aca="false">IF(N(E90)&gt;0,J90/E90,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R90" s="10" t="n">
+        <f aca="false">IF(N(E90)&gt;0,O90/E90,"")</f>
+        <v>10</v>
+      </c>
+      <c r="S90" s="8" t="n">
         <v>1490</v>
       </c>
-      <c r="Q90" s="8" t="n">
+      <c r="T90" s="8" t="n">
         <v>2240</v>
       </c>
-      <c r="R90" s="8" t="n">
+      <c r="U90" s="8" t="n">
         <v>2782</v>
       </c>
     </row>
@@ -6168,13 +7411,13 @@
         <v>46186</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>60</v>
@@ -6212,13 +7455,25 @@
         <f aca="false">K91+L91+M91+N91</f>
         <v>3135</v>
       </c>
-      <c r="P91" s="8" t="n">
+      <c r="P91" s="10" t="n">
+        <f aca="false">IF(N(E91)&gt;0,G91/E91,"")</f>
+        <v>32.25</v>
+      </c>
+      <c r="Q91" s="10" t="n">
+        <f aca="false">IF(N(E91)&gt;0,J91/E91,"")</f>
+        <v>20</v>
+      </c>
+      <c r="R91" s="10" t="n">
+        <f aca="false">IF(N(E91)&gt;0,O91/E91,"")</f>
+        <v>52.25</v>
+      </c>
+      <c r="S91" s="8" t="n">
         <v>627</v>
       </c>
-      <c r="Q91" s="8" t="n">
+      <c r="T91" s="8" t="n">
         <v>3968.1</v>
       </c>
-      <c r="R91" s="8" t="n">
+      <c r="U91" s="8" t="n">
         <v>3822</v>
       </c>
     </row>
@@ -6227,13 +7482,13 @@
         <v>46187</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>60</v>
@@ -6271,13 +7526,25 @@
         <f aca="false">K92+L92+M92+N92</f>
         <v>2040</v>
       </c>
-      <c r="P92" s="8" t="n">
+      <c r="P92" s="10" t="n">
+        <f aca="false">IF(N(E92)&gt;0,G92/E92,"")</f>
+        <v>34</v>
+      </c>
+      <c r="Q92" s="10" t="n">
+        <f aca="false">IF(N(E92)&gt;0,J92/E92,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R92" s="10" t="n">
+        <f aca="false">IF(N(E92)&gt;0,O92/E92,"")</f>
+        <v>34</v>
+      </c>
+      <c r="S92" s="8" t="n">
         <v>1643</v>
       </c>
-      <c r="Q92" s="8" t="n">
+      <c r="T92" s="8" t="n">
         <v>3805.4</v>
       </c>
-      <c r="R92" s="8" t="n">
+      <c r="U92" s="8" t="n">
         <v>3175</v>
       </c>
     </row>
@@ -6286,13 +7553,13 @@
         <v>46192</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>75</v>
@@ -6330,13 +7597,25 @@
         <f aca="false">K93+L93+M93+N93</f>
         <v>2845</v>
       </c>
-      <c r="P93" s="8" t="n">
+      <c r="P93" s="10" t="n">
+        <f aca="false">IF(N(E93)&gt;0,G93/E93,"")</f>
+        <v>23.2666666666667</v>
+      </c>
+      <c r="Q93" s="10" t="n">
+        <f aca="false">IF(N(E93)&gt;0,J93/E93,"")</f>
+        <v>8</v>
+      </c>
+      <c r="R93" s="10" t="n">
+        <f aca="false">IF(N(E93)&gt;0,O93/E93,"")</f>
+        <v>37.9333333333333</v>
+      </c>
+      <c r="S93" s="8" t="n">
         <v>1961.25</v>
       </c>
-      <c r="Q93" s="8" t="n">
+      <c r="T93" s="8" t="n">
         <v>4964.95</v>
       </c>
-      <c r="R93" s="8" t="n">
+      <c r="U93" s="8" t="n">
         <v>5102.25</v>
       </c>
     </row>
@@ -6345,13 +7624,13 @@
         <v>46193</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>37</v>
@@ -6389,13 +7668,25 @@
         <f aca="false">K94+L94+M94+N94</f>
         <v>1215</v>
       </c>
-      <c r="P94" s="8" t="n">
+      <c r="P94" s="10" t="n">
+        <f aca="false">IF(N(E94)&gt;0,G94/E94,"")</f>
+        <v>26.0810810810811</v>
+      </c>
+      <c r="Q94" s="10" t="n">
+        <f aca="false">IF(N(E94)&gt;0,J94/E94,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R94" s="10" t="n">
+        <f aca="false">IF(N(E94)&gt;0,O94/E94,"")</f>
+        <v>32.8378378378378</v>
+      </c>
+      <c r="S94" s="8" t="n">
         <v>1675.25</v>
       </c>
-      <c r="Q94" s="8" t="n">
+      <c r="T94" s="8" t="n">
         <v>2948.15</v>
       </c>
-      <c r="R94" s="8" t="n">
+      <c r="U94" s="8" t="n">
         <v>3009.75</v>
       </c>
     </row>
@@ -6404,13 +7695,13 @@
         <v>46197</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>25</v>
@@ -6448,13 +7739,25 @@
         <f aca="false">K95+L95+M95+N95</f>
         <v>2031</v>
       </c>
-      <c r="P95" s="8" t="n">
+      <c r="P95" s="10" t="n">
+        <f aca="false">IF(N(E95)&gt;0,G95/E95,"")</f>
+        <v>59.6</v>
+      </c>
+      <c r="Q95" s="10" t="n">
+        <f aca="false">IF(N(E95)&gt;0,J95/E95,"")</f>
+        <v>11.64</v>
+      </c>
+      <c r="R95" s="10" t="n">
+        <f aca="false">IF(N(E95)&gt;0,O95/E95,"")</f>
+        <v>81.24</v>
+      </c>
+      <c r="S95" s="8" t="n">
         <v>2363.95</v>
       </c>
-      <c r="Q95" s="8" t="n">
+      <c r="T95" s="8" t="n">
         <v>4510.54</v>
       </c>
-      <c r="R95" s="8" t="n">
+      <c r="U95" s="8" t="n">
         <v>3788.75</v>
       </c>
     </row>
@@ -6463,13 +7766,13 @@
         <v>46199</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>50</v>
@@ -6507,13 +7810,25 @@
         <f aca="false">K96+L96+M96+N96</f>
         <v>0</v>
       </c>
-      <c r="P96" s="8" t="n">
+      <c r="P96" s="10" t="n">
+        <f aca="false">IF(N(E96)&gt;0,G96/E96,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q96" s="10" t="n">
+        <f aca="false">IF(N(E96)&gt;0,J96/E96,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R96" s="10" t="n">
+        <f aca="false">IF(N(E96)&gt;0,O96/E96,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S96" s="8" t="n">
         <v>1305</v>
       </c>
-      <c r="Q96" s="8" t="n">
+      <c r="T96" s="8" t="n">
         <v>1305</v>
       </c>
-      <c r="R96" s="8" t="n">
+      <c r="U96" s="8" t="n">
         <v>1287</v>
       </c>
     </row>
@@ -6522,13 +7837,13 @@
         <v>46200</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>50</v>
@@ -6566,13 +7881,25 @@
         <f aca="false">K97+L97+M97+N97</f>
         <v>0</v>
       </c>
-      <c r="P97" s="8" t="n">
+      <c r="P97" s="10" t="n">
+        <f aca="false">IF(N(E97)&gt;0,G97/E97,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q97" s="10" t="n">
+        <f aca="false">IF(N(E97)&gt;0,J97/E97,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R97" s="10" t="n">
+        <f aca="false">IF(N(E97)&gt;0,O97/E97,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S97" s="8" t="n">
         <v>1305</v>
       </c>
-      <c r="Q97" s="8" t="n">
+      <c r="T97" s="8" t="n">
         <v>1305</v>
       </c>
-      <c r="R97" s="8" t="n">
+      <c r="U97" s="8" t="n">
         <v>2169.95</v>
       </c>
     </row>
@@ -6581,13 +7908,13 @@
         <v>46201</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>12</v>
@@ -6625,13 +7952,25 @@
         <f aca="false">K98+L98+M98+N98</f>
         <v>534</v>
       </c>
-      <c r="P98" s="8" t="n">
+      <c r="P98" s="10" t="n">
+        <f aca="false">IF(N(E98)&gt;0,G98/E98,"")</f>
+        <v>27.8333333333333</v>
+      </c>
+      <c r="Q98" s="10" t="n">
+        <f aca="false">IF(N(E98)&gt;0,J98/E98,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R98" s="10" t="n">
+        <f aca="false">IF(N(E98)&gt;0,O98/E98,"")</f>
+        <v>44.5</v>
+      </c>
+      <c r="S98" s="8" t="n">
         <v>524.4</v>
       </c>
-      <c r="Q98" s="8" t="n">
+      <c r="T98" s="8" t="n">
         <v>1078.44</v>
       </c>
-      <c r="R98" s="8" t="n">
+      <c r="U98" s="8" t="n">
         <v>3279</v>
       </c>
     </row>
@@ -6640,13 +7979,13 @@
         <v>46201</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>50</v>
@@ -6684,10 +8023,22 @@
         <f aca="false">K99+L99+M99+N99</f>
         <v>0</v>
       </c>
-      <c r="P99" s="8" t="n">
+      <c r="P99" s="10" t="n">
+        <f aca="false">IF(N(E99)&gt;0,G99/E99,"")</f>
+        <v>0</v>
+      </c>
+      <c r="Q99" s="10" t="n">
+        <f aca="false">IF(N(E99)&gt;0,J99/E99,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R99" s="10" t="n">
+        <f aca="false">IF(N(E99)&gt;0,O99/E99,"")</f>
+        <v>0</v>
+      </c>
+      <c r="S99" s="8" t="n">
         <v>1305</v>
       </c>
-      <c r="Q99" s="8" t="n">
+      <c r="T99" s="8" t="n">
         <v>1305</v>
       </c>
     </row>
@@ -6696,13 +8047,13 @@
         <v>46202</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>12</v>
@@ -6740,13 +8091,25 @@
         <f aca="false">K100+L100+M100+N100</f>
         <v>1343</v>
       </c>
-      <c r="P100" s="8" t="n">
+      <c r="P100" s="10" t="n">
+        <f aca="false">IF(N(E100)&gt;0,G100/E100,"")</f>
+        <v>95.25</v>
+      </c>
+      <c r="Q100" s="10" t="n">
+        <f aca="false">IF(N(E100)&gt;0,J100/E100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R100" s="10" t="n">
+        <f aca="false">IF(N(E100)&gt;0,O100/E100,"")</f>
+        <v>111.916666666667</v>
+      </c>
+      <c r="S100" s="8" t="n">
         <v>853.25</v>
       </c>
-      <c r="Q100" s="8" t="n">
+      <c r="T100" s="8" t="n">
         <v>2264.83</v>
       </c>
-      <c r="R100" s="8" t="n">
+      <c r="U100" s="8" t="n">
         <v>1991.25</v>
       </c>
     </row>
@@ -6755,13 +8118,13 @@
         <v>46203</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>12</v>
@@ -6799,80 +8162,107 @@
         <f aca="false">K101+L101+M101+N101</f>
         <v>857</v>
       </c>
-      <c r="P101" s="8" t="n">
+      <c r="P101" s="10" t="n">
+        <f aca="false">IF(N(E101)&gt;0,G101/E101,"")</f>
+        <v>54.75</v>
+      </c>
+      <c r="Q101" s="10" t="n">
+        <f aca="false">IF(N(E101)&gt;0,J101/E101,"")</f>
+        <v>0</v>
+      </c>
+      <c r="R101" s="10" t="n">
+        <f aca="false">IF(N(E101)&gt;0,O101/E101,"")</f>
+        <v>71.4166666666667</v>
+      </c>
+      <c r="S101" s="8" t="n">
         <v>617.45</v>
       </c>
-      <c r="Q101" s="8" t="n">
+      <c r="T101" s="8" t="n">
         <v>1513.87</v>
       </c>
-      <c r="R101" s="8" t="n">
+      <c r="U101" s="8" t="n">
         <v>1383.75</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="12" t="n">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="13" t="n">
+        <f aca="false">SUM(E5:E101)</f>
+        <v>5606</v>
+      </c>
+      <c r="F102" s="14" t="n">
         <f aca="false">SUM(F5:F101)</f>
         <v>79250</v>
       </c>
-      <c r="G102" s="12" t="n">
+      <c r="G102" s="14" t="n">
         <f aca="false">SUM(G5:G101)</f>
         <v>138981.52</v>
       </c>
-      <c r="H102" s="12" t="n">
+      <c r="H102" s="14" t="n">
         <f aca="false">SUM(H5:H101)</f>
         <v>86986.27</v>
       </c>
-      <c r="I102" s="12" t="n">
+      <c r="I102" s="14" t="n">
         <f aca="false">SUM(I5:I101)</f>
         <v>875</v>
       </c>
-      <c r="J102" s="12" t="n">
+      <c r="J102" s="14" t="n">
         <f aca="false">SUM(J5:J101)</f>
         <v>87861.27</v>
       </c>
-      <c r="K102" s="12" t="n">
+      <c r="K102" s="14" t="n">
         <f aca="false">SUM(K5:K101)</f>
         <v>226842.79</v>
       </c>
-      <c r="L102" s="12" t="n">
+      <c r="L102" s="14" t="n">
         <f aca="false">SUM(L5:L101)</f>
         <v>16305.58</v>
       </c>
-      <c r="M102" s="12" t="n">
+      <c r="M102" s="14" t="n">
         <f aca="false">SUM(M5:M101)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="12" t="n">
+      <c r="N102" s="14" t="n">
         <f aca="false">SUM(N5:N101)</f>
         <v>59780.14</v>
       </c>
-      <c r="O102" s="12" t="n">
+      <c r="O102" s="14" t="n">
         <f aca="false">SUM(O5:O101)</f>
         <v>302928.51</v>
       </c>
-      <c r="P102" s="12" t="n">
-        <f aca="false">SUM(P5:P101)</f>
+      <c r="P102" s="15" t="n">
+        <f aca="false">IF(N(E102)&gt;0,G102/E102,"")</f>
+        <v>24.7915661790938</v>
+      </c>
+      <c r="Q102" s="15" t="n">
+        <f aca="false">IF(N(E102)&gt;0,J102/E102,"")</f>
+        <v>15.6727202996789</v>
+      </c>
+      <c r="R102" s="15" t="n">
+        <f aca="false">IF(N(E102)&gt;0,O102/E102,"")</f>
+        <v>54.0364805565466</v>
+      </c>
+      <c r="S102" s="14" t="n">
+        <f aca="false">SUM(S5:S101)</f>
         <v>86184.66</v>
       </c>
-      <c r="Q102" s="12" t="n">
-        <f aca="false">SUM(Q5:Q101)</f>
+      <c r="T102" s="14" t="n">
+        <f aca="false">SUM(T5:T101)</f>
         <v>396244.9</v>
       </c>
-      <c r="R102" s="12" t="n">
-        <f aca="false">SUM(R5:R101)</f>
+      <c r="U102" s="14" t="n">
+        <f aca="false">SUM(U5:U101)</f>
         <v>350548.27</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="13" t="s">
-        <v>114</v>
+      <c r="B104" s="16" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -6908,7 +8298,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6916,25 +8306,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6942,10 +8332,10 @@
         <v>45841</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>1</v>
@@ -6961,7 +8351,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6969,10 +8359,10 @@
         <v>45843</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>1</v>
@@ -6988,7 +8378,7 @@
         <v>537.379999999999</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6996,7 +8386,7 @@
         <v>45847</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7"/>
@@ -7009,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7017,7 +8407,7 @@
         <v>45848</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="7"/>
@@ -7030,7 +8420,7 @@
         <v>401.5</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7038,10 +8428,10 @@
         <v>45849</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>2</v>
@@ -7057,7 +8447,7 @@
         <v>-275.4</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7065,7 +8455,7 @@
         <v>45850</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>
@@ -7078,7 +8468,7 @@
         <v>896</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7086,7 +8476,7 @@
         <v>45851</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="7"/>
@@ -7099,7 +8489,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7107,7 +8497,7 @@
         <v>45855</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="7"/>
@@ -7120,7 +8510,7 @@
         <v>1230</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7128,10 +8518,10 @@
         <v>45856</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>1</v>
@@ -7147,7 +8537,7 @@
         <v>896</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7155,7 +8545,7 @@
         <v>45857</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
@@ -7168,7 +8558,7 @@
         <v>1997</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7176,10 +8566,10 @@
         <v>45860</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1</v>
@@ -7195,7 +8585,7 @@
         <v>625.9</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7203,10 +8593,10 @@
         <v>45861</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1</v>
@@ -7220,7 +8610,7 @@
         <v>-4690</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7228,10 +8618,10 @@
         <v>45862</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>1</v>
@@ -7247,7 +8637,7 @@
         <v>5037</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7255,10 +8645,10 @@
         <v>45863</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1</v>
@@ -7274,7 +8664,7 @@
         <v>-1415.82</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7282,7 +8672,7 @@
         <v>45864</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
@@ -7295,7 +8685,7 @@
         <v>440.4</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7303,10 +8693,10 @@
         <v>45865</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1</v>
@@ -7322,7 +8712,7 @@
         <v>270.5</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7330,10 +8720,10 @@
         <v>45870</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -7349,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7357,10 +8747,10 @@
         <v>45871</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -7376,7 +8766,7 @@
         <v>2998.5</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7384,10 +8774,10 @@
         <v>45878</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -7403,7 +8793,7 @@
         <v>277.25</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7411,7 +8801,7 @@
         <v>45880</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="7"/>
@@ -7424,7 +8814,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7432,10 +8822,10 @@
         <v>45887</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1</v>
@@ -7451,7 +8841,7 @@
         <v>384.09</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7459,10 +8849,10 @@
         <v>45891</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1</v>
@@ -7478,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7486,10 +8876,10 @@
         <v>45894</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>1</v>
@@ -7503,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,7 +8901,7 @@
         <v>45896</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="7"/>
@@ -7524,7 +8914,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7532,7 +8922,7 @@
         <v>45898</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="7"/>
@@ -7545,7 +8935,7 @@
         <v>1078</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7553,10 +8943,10 @@
         <v>45899</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1</v>
@@ -7572,7 +8962,7 @@
         <v>3235.75</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7580,10 +8970,10 @@
         <v>45905</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>1</v>
@@ -7599,7 +8989,7 @@
         <v>-1291.54</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7607,10 +8997,10 @@
         <v>45912</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>1</v>
@@ -7626,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7634,7 +9024,7 @@
         <v>45913</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="7"/>
@@ -7647,7 +9037,7 @@
         <v>2023</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7655,10 +9045,10 @@
         <v>45916</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>1</v>
@@ -7674,7 +9064,7 @@
         <v>193.8</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7682,7 +9072,7 @@
         <v>45919</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
@@ -7695,7 +9085,7 @@
         <v>469</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7703,10 +9093,10 @@
         <v>45920</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>1</v>
@@ -7722,7 +9112,7 @@
         <v>2443.75</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7730,10 +9120,10 @@
         <v>45924</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
@@ -7747,7 +9137,7 @@
         <v>-146</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7755,7 +9145,7 @@
         <v>45925</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="7"/>
@@ -7768,7 +9158,7 @@
         <v>658.4</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7776,10 +9166,10 @@
         <v>45926</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>1</v>
@@ -7793,7 +9183,7 @@
         <v>-4450</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7801,7 +9191,7 @@
         <v>45927</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
@@ -7814,7 +9204,7 @@
         <v>182</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7822,10 +9212,10 @@
         <v>45930</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>1</v>
@@ -7841,7 +9231,7 @@
         <v>69.35</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,10 +9239,10 @@
         <v>45932</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -7868,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7876,10 +9266,10 @@
         <v>45933</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>1</v>
@@ -7895,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7903,7 +9293,7 @@
         <v>45934</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="7"/>
@@ -7916,7 +9306,7 @@
         <v>214.5</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7924,10 +9314,10 @@
         <v>45951</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>2</v>
@@ -7943,7 +9333,7 @@
         <v>306.32</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7951,7 +9341,7 @@
         <v>45953</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="7"/>
@@ -7964,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7972,10 +9362,10 @@
         <v>45959</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>1</v>
@@ -7991,7 +9381,7 @@
         <v>1580.5</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7999,7 +9389,7 @@
         <v>45967</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="7"/>
@@ -8012,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8020,7 +9410,7 @@
         <v>45968</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="7"/>
@@ -8033,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8041,7 +9431,7 @@
         <v>45973</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="7"/>
@@ -8054,7 +9444,7 @@
         <v>12.5</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8062,7 +9452,7 @@
         <v>45975</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
@@ -8075,7 +9465,7 @@
         <v>8</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8083,7 +9473,7 @@
         <v>45976</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
@@ -8096,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8104,7 +9494,7 @@
         <v>45977</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="7"/>
@@ -8117,7 +9507,7 @@
         <v>23</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8125,7 +9515,7 @@
         <v>45978</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="7"/>
@@ -8138,7 +9528,7 @@
         <v>39</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8146,10 +9536,10 @@
         <v>45981</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>1</v>
@@ -8165,7 +9555,7 @@
         <v>49.75</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8173,10 +9563,10 @@
         <v>45982</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>1</v>
@@ -8192,7 +9582,7 @@
         <v>-219.73</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8200,7 +9590,7 @@
         <v>45983</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="7"/>
@@ -8213,7 +9603,7 @@
         <v>93</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8221,7 +9611,7 @@
         <v>45984</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="7"/>
@@ -8234,7 +9624,7 @@
         <v>35.25</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8242,7 +9632,7 @@
         <v>45987</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="7"/>
@@ -8255,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8263,10 +9653,10 @@
         <v>45988</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>1</v>
@@ -8280,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8288,10 +9678,10 @@
         <v>45989</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>1</v>
@@ -8305,7 +9695,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8313,10 +9703,10 @@
         <v>45994</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>1</v>
@@ -8332,7 +9722,7 @@
         <v>238.65</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8340,10 +9730,10 @@
         <v>45995</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>1</v>
@@ -8359,7 +9749,7 @@
         <v>253.5</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8367,7 +9757,7 @@
         <v>45996</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="7"/>
@@ -8380,7 +9770,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8388,7 +9778,7 @@
         <v>45997</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="7"/>
@@ -8401,7 +9791,7 @@
         <v>56</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8409,7 +9799,7 @@
         <v>46000</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="7"/>
@@ -8422,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8430,10 +9820,10 @@
         <v>46002</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>1</v>
@@ -8449,7 +9839,7 @@
         <v>-206.3</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8457,7 +9847,7 @@
         <v>46003</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="7"/>
@@ -8470,7 +9860,7 @@
         <v>660</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8478,10 +9868,10 @@
         <v>46005</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1</v>
@@ -8497,7 +9887,7 @@
         <v>818.25</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8505,7 +9895,7 @@
         <v>46006</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="7"/>
@@ -8518,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8526,7 +9916,7 @@
         <v>46008</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="7"/>
@@ -8539,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8547,10 +9937,10 @@
         <v>46012</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>1</v>
@@ -8566,7 +9956,7 @@
         <v>693.25</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8574,7 +9964,7 @@
         <v>46013</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="7"/>
@@ -8587,7 +9977,7 @@
         <v>6.25</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,7 +9985,7 @@
         <v>46014</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="7"/>
@@ -8608,7 +9998,7 @@
         <v>2</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8616,7 +10006,7 @@
         <v>46017</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="7"/>
@@ -8629,7 +10019,7 @@
         <v>27.5</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8637,7 +10027,7 @@
         <v>46018</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="7"/>
@@ -8650,7 +10040,7 @@
         <v>3</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8658,7 +10048,7 @@
         <v>46019</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C77" s="6"/>
       <c r="D77" s="7"/>
@@ -8671,7 +10061,7 @@
         <v>20</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8679,10 +10069,10 @@
         <v>46031</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>1</v>
@@ -8698,7 +10088,7 @@
         <v>126.3</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8706,10 +10096,10 @@
         <v>46032</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>1</v>
@@ -8725,7 +10115,7 @@
         <v>430.6</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8733,10 +10123,10 @@
         <v>46033</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -8752,7 +10142,7 @@
         <v>-415.98</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8760,10 +10150,10 @@
         <v>46038</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -8779,7 +10169,7 @@
         <v>147.75</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8787,10 +10177,10 @@
         <v>46040</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -8806,7 +10196,7 @@
         <v>146.45</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8814,10 +10204,10 @@
         <v>46041</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>1</v>
@@ -8833,7 +10223,7 @@
         <v>1565.9</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8841,10 +10231,10 @@
         <v>46042</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>1</v>
@@ -8860,7 +10250,7 @@
         <v>165.9</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8868,10 +10258,10 @@
         <v>46043</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>1</v>
@@ -8887,7 +10277,7 @@
         <v>223.9</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8895,10 +10285,10 @@
         <v>46044</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1</v>
@@ -8914,7 +10304,7 @@
         <v>236.9</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8922,10 +10312,10 @@
         <v>46045</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>2</v>
@@ -8941,7 +10331,7 @@
         <v>307.4</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8949,10 +10339,10 @@
         <v>46051</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>1</v>
@@ -8968,7 +10358,7 @@
         <v>56</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8976,10 +10366,10 @@
         <v>46052</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>1</v>
@@ -8995,7 +10385,7 @@
         <v>-108.57</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9003,10 +10393,10 @@
         <v>46055</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>1</v>
@@ -9022,7 +10412,7 @@
         <v>350.75</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9030,10 +10420,10 @@
         <v>46060</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>1</v>
@@ -9049,7 +10439,7 @@
         <v>625.25</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9057,10 +10447,10 @@
         <v>46066</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>1</v>
@@ -9076,7 +10466,7 @@
         <v>-6961.8</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9084,7 +10474,7 @@
         <v>46067</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="7"/>
@@ -9097,7 +10487,7 @@
         <v>5239.27</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9105,10 +10495,10 @@
         <v>46081</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1</v>
@@ -9124,7 +10514,7 @@
         <v>154</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9132,10 +10522,10 @@
         <v>46082</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -9151,7 +10541,7 @@
         <v>1370.6</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9159,10 +10549,10 @@
         <v>46085</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>1</v>
@@ -9178,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9186,10 +10576,10 @@
         <v>46086</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>1</v>
@@ -9205,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9213,10 +10603,10 @@
         <v>46088</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>1</v>
@@ -9232,7 +10622,7 @@
         <v>499.950000000001</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9240,10 +10630,10 @@
         <v>46091</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>1</v>
@@ -9259,7 +10649,7 @@
         <v>14.9000000000001</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9267,10 +10657,10 @@
         <v>46092</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1</v>
@@ -9286,7 +10676,7 @@
         <v>-135</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9294,10 +10684,10 @@
         <v>46095</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D101" s="7" t="n">
         <v>1</v>
@@ -9313,7 +10703,7 @@
         <v>-526.88</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9321,10 +10711,10 @@
         <v>46096</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1</v>
@@ -9340,7 +10730,7 @@
         <v>-103</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9348,7 +10738,7 @@
         <v>46099</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C103" s="6"/>
       <c r="D103" s="7"/>
@@ -9361,7 +10751,7 @@
         <v>13.5</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9369,10 +10759,10 @@
         <v>46100</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1</v>
@@ -9388,7 +10778,7 @@
         <v>50.4000000000001</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9396,10 +10786,10 @@
         <v>46101</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D105" s="7" t="n">
         <v>1</v>
@@ -9415,7 +10805,7 @@
         <v>474.75</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9423,10 +10813,10 @@
         <v>46102</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>2</v>
@@ -9442,7 +10832,7 @@
         <v>-1676</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9450,10 +10840,10 @@
         <v>46109</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>1</v>
@@ -9467,7 +10857,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9475,7 +10865,7 @@
         <v>46111</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="7"/>
@@ -9488,7 +10878,7 @@
         <v>500</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9496,7 +10886,7 @@
         <v>46115</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C109" s="6"/>
       <c r="D109" s="7"/>
@@ -9509,7 +10899,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9517,7 +10907,7 @@
         <v>46121</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="7"/>
@@ -9530,7 +10920,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9538,10 +10928,10 @@
         <v>46122</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9557,7 +10947,7 @@
         <v>245.92</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9565,10 +10955,10 @@
         <v>46124</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9584,7 +10974,7 @@
         <v>337.5</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9592,10 +10982,10 @@
         <v>46136</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9611,7 +11001,7 @@
         <v>430</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9619,10 +11009,10 @@
         <v>46137</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>1</v>
@@ -9638,7 +11028,7 @@
         <v>2325.75</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9646,10 +11036,10 @@
         <v>46147</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>1</v>
@@ -9665,7 +11055,7 @@
         <v>1412.5</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9673,10 +11063,10 @@
         <v>46149</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9692,7 +11082,7 @@
         <v>51.25</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,10 +11090,10 @@
         <v>46154</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9719,7 +11109,7 @@
         <v>474.25</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9727,10 +11117,10 @@
         <v>46155</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1</v>
@@ -9746,7 +11136,7 @@
         <v>1979.75</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9754,10 +11144,10 @@
         <v>46156</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>1</v>
@@ -9773,7 +11163,7 @@
         <v>1723.75</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9781,10 +11171,10 @@
         <v>46157</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1</v>
@@ -9800,7 +11190,7 @@
         <v>1849.25</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9808,10 +11198,10 @@
         <v>46162</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9827,7 +11217,7 @@
         <v>2966</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9835,10 +11225,10 @@
         <v>46163</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>1</v>
@@ -9854,7 +11244,7 @@
         <v>1267</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9862,7 +11252,7 @@
         <v>46165</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C123" s="6"/>
       <c r="D123" s="7"/>
@@ -9875,7 +11265,7 @@
         <v>348.3</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9883,7 +11273,7 @@
         <v>46166</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="7"/>
@@ -9896,7 +11286,7 @@
         <v>121</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9904,10 +11294,10 @@
         <v>46172</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>1</v>
@@ -9923,7 +11313,7 @@
         <v>-1363</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9931,10 +11321,10 @@
         <v>46173</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>1</v>
@@ -9950,7 +11340,7 @@
         <v>2198.75</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9958,7 +11348,7 @@
         <v>46174</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C127" s="6"/>
       <c r="D127" s="7"/>
@@ -9971,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9979,10 +11369,10 @@
         <v>46175</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>1</v>
@@ -9998,7 +11388,7 @@
         <v>3779.45</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10006,10 +11396,10 @@
         <v>46179</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D129" s="7" t="n">
         <v>1</v>
@@ -10025,7 +11415,7 @@
         <v>1709.77</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10033,10 +11423,10 @@
         <v>46180</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10052,7 +11442,7 @@
         <v>3956</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10060,10 +11450,10 @@
         <v>46185</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>1</v>
@@ -10079,7 +11469,7 @@
         <v>2032</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10087,10 +11477,10 @@
         <v>46186</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10106,7 +11496,7 @@
         <v>687</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10114,10 +11504,10 @@
         <v>46187</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10133,7 +11523,7 @@
         <v>1135</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10141,10 +11531,10 @@
         <v>46192</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1</v>
@@ -10160,7 +11550,7 @@
         <v>2257.25</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10168,10 +11558,10 @@
         <v>46193</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>1</v>
@@ -10187,7 +11577,7 @@
         <v>1794.75</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10195,10 +11585,10 @@
         <v>46197</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1</v>
@@ -10214,7 +11604,7 @@
         <v>1757.75</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10222,10 +11612,10 @@
         <v>46199</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>1</v>
@@ -10241,7 +11631,7 @@
         <v>1287</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10249,10 +11639,10 @@
         <v>46200</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>1</v>
@@ -10268,7 +11658,7 @@
         <v>2169.95</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10276,10 +11666,10 @@
         <v>46201</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D139" s="7" t="n">
         <v>2</v>
@@ -10295,7 +11685,7 @@
         <v>2745</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10303,10 +11693,10 @@
         <v>46202</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1</v>
@@ -10322,7 +11712,7 @@
         <v>648.25</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10330,10 +11720,10 @@
         <v>46203</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>1</v>
@@ -10349,29 +11739,29 @@
         <v>526.75</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="11"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D142" s="11"/>
-      <c r="E142" s="12" t="n">
+      <c r="A142" s="12"/>
+      <c r="B142" s="12"/>
+      <c r="C142" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D142" s="12"/>
+      <c r="E142" s="14" t="n">
         <f aca="false">SUM(E5:E141)</f>
         <v>302928.51</v>
       </c>
-      <c r="F142" s="12" t="n">
+      <c r="F142" s="14" t="n">
         <f aca="false">SUM(F5:F141)</f>
         <v>367436.64</v>
       </c>
-      <c r="G142" s="12" t="n">
+      <c r="G142" s="14" t="n">
         <f aca="false">SUM(G5:G141)</f>
         <v>64508.13</v>
       </c>
-      <c r="H142" s="11"/>
+      <c r="H142" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10404,31 +11794,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="A4" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>159</v>
+      <c r="A5" s="18"/>
+      <c r="B5" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10445,13 +11835,13 @@
         <f aca="false">C6-B6</f>
         <v>3142.53</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="21" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>86986.27</v>
@@ -10463,13 +11853,13 @@
         <f aca="false">C7-B7</f>
         <v>6225.31</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>161</v>
+      <c r="E7" s="21" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>875</v>
@@ -10481,13 +11871,13 @@
         <f aca="false">C8-B8</f>
         <v>56769.99</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>163</v>
+      <c r="E8" s="21" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>76085.72</v>
@@ -10499,13 +11889,13 @@
         <f aca="false">C9-B9</f>
         <v>-2280.7</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>165</v>
+      <c r="E9" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>0</v>
@@ -10517,40 +11907,40 @@
         <f aca="false">C10-B10</f>
         <v>651</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>167</v>
+      <c r="E10" s="21" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="12" t="n">
+      <c r="A11" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="14" t="n">
         <f aca="false">SUM(B6:B10)</f>
         <v>302928.51</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="14" t="n">
         <f aca="false">SUM(C6:C10)</f>
         <v>367436.64</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="14" t="n">
         <f aca="false">C11-B11</f>
         <v>64508.13</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>169</v>
+      <c r="A14" s="18" t="s">
+        <v>172</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>302928.51</v>
@@ -10558,7 +11948,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>-9286</v>
@@ -10566,7 +11956,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>56905.76</v>
@@ -10574,69 +11964,758 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>16888.37</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18" s="12" t="n">
+      <c r="A18" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="14" t="n">
         <f aca="false">SUM(B14:B17)</f>
         <v>367436.64</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>367436.64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>176</v>
+      <c r="A22" s="22" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>177</v>
+      <c r="A23" s="22" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>178</v>
+      <c r="A24" s="22" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>179</v>
+      <c r="A25" s="22" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>180</v>
+      <c r="A26" s="22" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>181</v>
+      <c r="A27" s="22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>147</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>15825</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>6358.68</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>2232</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>2042.04</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>52</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1341</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>125</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1276.02</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>1170</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>1152</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>980</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>840</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>680</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>480</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B39" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>1766.25</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="14" t="n">
+        <f aca="false">SUM(C5:C42)</f>
+        <v>60237.99</v>
+      </c>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>52854.74</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>4346.25</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>136029.33</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>4346.25</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>86986.27</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="22" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
